--- a/research/traditional_assets/database/data/indonesia/indonesia_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_publishing_newspapers.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1131338539393098</v>
+        <v>0.1129200594606434</v>
       </c>
       <c r="C2">
-        <v>96.68199648223032</v>
+        <v>95.93522724049406</v>
       </c>
       <c r="D2">
-        <v>80.58199648223031</v>
+        <v>80.80232724049407</v>
       </c>
       <c r="E2">
-        <v>-3.21</v>
+        <v>-2.242900000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9671</v>
       </c>
       <c r="G2">
         <v>16.1</v>
@@ -1707,28 +1707,28 @@
         <v>16.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04864512999999999</v>
       </c>
       <c r="N2">
-        <v>16.7</v>
+        <v>16.65135487</v>
       </c>
       <c r="O2">
-        <v>3.674</v>
+        <v>3.6632980714</v>
       </c>
       <c r="P2">
-        <v>13.026</v>
+        <v>12.9880567986</v>
       </c>
       <c r="Q2">
-        <v>15.526</v>
+        <v>15.4880567986</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1131338539393098</v>
+        <v>0.1136643630915589</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226994</v>
+        <v>0.987509173193666</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>343.3026080925264</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1129200594606434</v>
+        <v>0.1127062649819769</v>
       </c>
       <c r="C3">
-        <v>95.93522724049406</v>
+        <v>95.1896661778716</v>
       </c>
       <c r="D3">
-        <v>80.80232724049407</v>
+        <v>81.0238661778716</v>
       </c>
       <c r="E3">
-        <v>-2.242900000000001</v>
+        <v>-1.2758</v>
       </c>
       <c r="F3">
-        <v>0.9671</v>
+        <v>1.9342</v>
       </c>
       <c r="G3">
         <v>16.1</v>
@@ -1789,28 +1789,28 @@
         <v>16.7</v>
       </c>
       <c r="M3">
-        <v>0.04864512999999999</v>
+        <v>0.09729025999999999</v>
       </c>
       <c r="N3">
-        <v>16.65135487</v>
+        <v>16.60270974</v>
       </c>
       <c r="O3">
-        <v>3.6632980714</v>
+        <v>3.6525961428</v>
       </c>
       <c r="P3">
-        <v>12.9880567986</v>
+        <v>12.9501135972</v>
       </c>
       <c r="Q3">
-        <v>15.4880567986</v>
+        <v>15.4501135972</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1136643630915589</v>
+        <v>0.1142056989612009</v>
       </c>
       <c r="T3">
-        <v>0.987509173193666</v>
+        <v>0.9953862696946526</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>343.3026080925264</v>
+        <v>171.6513040462632</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1127062649819769</v>
+        <v>0.1124924705033104</v>
       </c>
       <c r="C4">
-        <v>95.1896661778716</v>
+        <v>94.44532325922133</v>
       </c>
       <c r="D4">
-        <v>81.0238661778716</v>
+        <v>81.24662325922134</v>
       </c>
       <c r="E4">
-        <v>-1.2758</v>
+        <v>-0.3087000000000009</v>
       </c>
       <c r="F4">
-        <v>1.9342</v>
+        <v>2.9013</v>
       </c>
       <c r="G4">
         <v>16.1</v>
@@ -1871,28 +1871,28 @@
         <v>16.7</v>
       </c>
       <c r="M4">
-        <v>0.09729025999999999</v>
+        <v>0.14593539</v>
       </c>
       <c r="N4">
-        <v>16.60270974</v>
+        <v>16.55406461</v>
       </c>
       <c r="O4">
-        <v>3.6525961428</v>
+        <v>3.6418942142</v>
       </c>
       <c r="P4">
-        <v>12.9501135972</v>
+        <v>12.9121703958</v>
       </c>
       <c r="Q4">
-        <v>15.4501135972</v>
+        <v>15.4121703958</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1142056989612009</v>
+        <v>0.1147581963951654</v>
       </c>
       <c r="T4">
-        <v>0.9953862696946526</v>
+        <v>1.003425780556484</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>171.6513040462632</v>
+        <v>114.4342026975088</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1124924705033104</v>
+        <v>0.1122786760246439</v>
       </c>
       <c r="C5">
-        <v>94.44532325922133</v>
+        <v>93.70220855928851</v>
       </c>
       <c r="D5">
-        <v>81.24662325922134</v>
+        <v>81.47060855928851</v>
       </c>
       <c r="E5">
-        <v>-0.3087000000000009</v>
+        <v>0.6583999999999994</v>
       </c>
       <c r="F5">
-        <v>2.9013</v>
+        <v>3.8684</v>
       </c>
       <c r="G5">
         <v>16.1</v>
@@ -1953,28 +1953,28 @@
         <v>16.7</v>
       </c>
       <c r="M5">
-        <v>0.14593539</v>
+        <v>0.19458052</v>
       </c>
       <c r="N5">
-        <v>16.55406461</v>
+        <v>16.50541948</v>
       </c>
       <c r="O5">
-        <v>3.6418942142</v>
+        <v>3.6311922856</v>
       </c>
       <c r="P5">
-        <v>12.9121703958</v>
+        <v>12.8742271944</v>
       </c>
       <c r="Q5">
-        <v>15.4121703958</v>
+        <v>15.3742271944</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1147581963951654</v>
+        <v>0.1153222041923374</v>
       </c>
       <c r="T5">
-        <v>1.003425780556484</v>
+        <v>1.011632781227937</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>114.4342026975088</v>
+        <v>85.82565202313162</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1122786760246439</v>
+        <v>0.1120648815459774</v>
       </c>
       <c r="C6">
-        <v>93.70220855928851</v>
+        <v>92.96033226422404</v>
       </c>
       <c r="D6">
-        <v>81.47060855928851</v>
+        <v>81.69583226422404</v>
       </c>
       <c r="E6">
-        <v>0.6583999999999994</v>
+        <v>1.625499999999999</v>
       </c>
       <c r="F6">
-        <v>3.8684</v>
+        <v>4.8355</v>
       </c>
       <c r="G6">
         <v>16.1</v>
@@ -2035,28 +2035,28 @@
         <v>16.7</v>
       </c>
       <c r="M6">
-        <v>0.19458052</v>
+        <v>0.24322565</v>
       </c>
       <c r="N6">
-        <v>16.50541948</v>
+        <v>16.45677435</v>
       </c>
       <c r="O6">
-        <v>3.6311922856</v>
+        <v>3.620490357</v>
       </c>
       <c r="P6">
-        <v>12.8742271944</v>
+        <v>12.836283993</v>
       </c>
       <c r="Q6">
-        <v>15.3742271944</v>
+        <v>15.336283993</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1153222041923374</v>
+        <v>0.115898085837871</v>
       </c>
       <c r="T6">
-        <v>1.011632781227937</v>
+        <v>1.020012560860895</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.82565202313162</v>
+        <v>68.6605216185053</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1120648815459774</v>
+        <v>0.1118510870673109</v>
       </c>
       <c r="C7">
-        <v>92.96033226422404</v>
+        <v>92.21970467312856</v>
       </c>
       <c r="D7">
-        <v>81.69583226422404</v>
+        <v>81.92230467312856</v>
       </c>
       <c r="E7">
-        <v>1.625499999999999</v>
+        <v>2.5926</v>
       </c>
       <c r="F7">
-        <v>4.8355</v>
+        <v>5.8026</v>
       </c>
       <c r="G7">
         <v>16.1</v>
@@ -2117,28 +2117,28 @@
         <v>16.7</v>
       </c>
       <c r="M7">
-        <v>0.24322565</v>
+        <v>0.29187078</v>
       </c>
       <c r="N7">
-        <v>16.45677435</v>
+        <v>16.40812922</v>
       </c>
       <c r="O7">
-        <v>3.620490357</v>
+        <v>3.6097884284</v>
       </c>
       <c r="P7">
-        <v>12.836283993</v>
+        <v>12.7983407916</v>
       </c>
       <c r="Q7">
-        <v>15.336283993</v>
+        <v>15.2983407916</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.115898085837871</v>
+        <v>0.1164862202843733</v>
       </c>
       <c r="T7">
-        <v>1.020012560860895</v>
+        <v>1.028570633677532</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.6605216185053</v>
+        <v>57.2171013487544</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1118510870673109</v>
+        <v>0.1116372925886445</v>
       </c>
       <c r="C8">
-        <v>92.21970467312856</v>
+        <v>91.48033619962243</v>
       </c>
       <c r="D8">
-        <v>81.92230467312856</v>
+        <v>82.15003619962243</v>
       </c>
       <c r="E8">
-        <v>2.592599999999999</v>
+        <v>3.559699999999998</v>
       </c>
       <c r="F8">
-        <v>5.802599999999999</v>
+        <v>6.769699999999998</v>
       </c>
       <c r="G8">
         <v>16.1</v>
@@ -2199,28 +2199,28 @@
         <v>16.7</v>
       </c>
       <c r="M8">
-        <v>0.2918707799999999</v>
+        <v>0.3405159099999999</v>
       </c>
       <c r="N8">
-        <v>16.40812922</v>
+        <v>16.35948409</v>
       </c>
       <c r="O8">
-        <v>3.6097884284</v>
+        <v>3.5990864998</v>
       </c>
       <c r="P8">
-        <v>12.7983407916</v>
+        <v>12.7603975902</v>
       </c>
       <c r="Q8">
-        <v>15.2983407916</v>
+        <v>15.2603975902</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1164862202843733</v>
+        <v>0.1170870027834887</v>
       </c>
       <c r="T8">
-        <v>1.028570633677532</v>
+        <v>1.037312751070871</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>57.21710134875441</v>
+        <v>49.04322972750379</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1116372925886445</v>
+        <v>0.111423498109978</v>
       </c>
       <c r="C9">
-        <v>91.48033619962246</v>
+        <v>90.74223737344202</v>
       </c>
       <c r="D9">
-        <v>82.15003619962245</v>
+        <v>82.37903737344202</v>
       </c>
       <c r="E9">
-        <v>3.5597</v>
+        <v>4.5268</v>
       </c>
       <c r="F9">
-        <v>6.7697</v>
+        <v>7.7368</v>
       </c>
       <c r="G9">
         <v>16.1</v>
@@ -2281,28 +2281,28 @@
         <v>16.7</v>
       </c>
       <c r="M9">
-        <v>0.34051591</v>
+        <v>0.38916104</v>
       </c>
       <c r="N9">
-        <v>16.35948409</v>
+        <v>16.31083896</v>
       </c>
       <c r="O9">
-        <v>3.5990864998</v>
+        <v>3.5883845712</v>
       </c>
       <c r="P9">
-        <v>12.7603975902</v>
+        <v>12.7224543888</v>
       </c>
       <c r="Q9">
-        <v>15.2603975902</v>
+        <v>15.2224543888</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1170870027834887</v>
+        <v>0.1177008457717152</v>
       </c>
       <c r="T9">
-        <v>1.037312751070871</v>
+        <v>1.0462449144945</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>49.04322972750377</v>
+        <v>42.91282601156581</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.111423498109978</v>
+        <v>0.1112097036313115</v>
       </c>
       <c r="C10">
-        <v>90.74223737344202</v>
+        <v>90.0054188420624</v>
       </c>
       <c r="D10">
-        <v>82.37903737344202</v>
+        <v>82.60931884206239</v>
       </c>
       <c r="E10">
-        <v>4.5268</v>
+        <v>5.493899999999998</v>
       </c>
       <c r="F10">
-        <v>7.7368</v>
+        <v>8.703899999999999</v>
       </c>
       <c r="G10">
         <v>16.1</v>
@@ -2363,28 +2363,28 @@
         <v>16.7</v>
       </c>
       <c r="M10">
-        <v>0.38916104</v>
+        <v>0.4378061699999999</v>
       </c>
       <c r="N10">
-        <v>16.31083896</v>
+        <v>16.26219383</v>
       </c>
       <c r="O10">
-        <v>3.5883845712</v>
+        <v>3.5776826426</v>
       </c>
       <c r="P10">
-        <v>12.7224543888</v>
+        <v>12.6845111874</v>
       </c>
       <c r="Q10">
-        <v>15.2224543888</v>
+        <v>15.1845111874</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1177008457717152</v>
+        <v>0.118328179814628</v>
       </c>
       <c r="T10">
-        <v>1.0462449144945</v>
+        <v>1.055373389202165</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.91282601156581</v>
+        <v>38.14473423250294</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1112097036313115</v>
+        <v>0.110995909152645</v>
       </c>
       <c r="C11">
-        <v>90.0054188420624</v>
+        <v>89.26989137234787</v>
       </c>
       <c r="D11">
-        <v>82.60931884206239</v>
+        <v>82.84089137234787</v>
       </c>
       <c r="E11">
-        <v>5.493899999999998</v>
+        <v>6.460999999999999</v>
       </c>
       <c r="F11">
-        <v>8.703899999999999</v>
+        <v>9.670999999999999</v>
       </c>
       <c r="G11">
         <v>16.1</v>
@@ -2445,28 +2445,28 @@
         <v>16.7</v>
       </c>
       <c r="M11">
-        <v>0.4378061699999999</v>
+        <v>0.4864512999999999</v>
       </c>
       <c r="N11">
-        <v>16.26219383</v>
+        <v>16.2135487</v>
       </c>
       <c r="O11">
-        <v>3.5776826426</v>
+        <v>3.566980714</v>
       </c>
       <c r="P11">
-        <v>12.6845111874</v>
+        <v>12.646567986</v>
       </c>
       <c r="Q11">
-        <v>15.1845111874</v>
+        <v>15.146567986</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.118328179814628</v>
+        <v>0.11896945461405</v>
       </c>
       <c r="T11">
-        <v>1.055373389202165</v>
+        <v>1.064704718903333</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>38.14473423250294</v>
+        <v>34.33026080925265</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.110995909152645</v>
+        <v>0.1107821146739785</v>
       </c>
       <c r="C12">
-        <v>89.26989137234787</v>
+        <v>88.53566585222974</v>
       </c>
       <c r="D12">
-        <v>82.84089137234787</v>
+        <v>83.07376585222973</v>
       </c>
       <c r="E12">
-        <v>6.460999999999999</v>
+        <v>7.428099999999999</v>
       </c>
       <c r="F12">
-        <v>9.670999999999999</v>
+        <v>10.6381</v>
       </c>
       <c r="G12">
         <v>16.1</v>
@@ -2527,28 +2527,28 @@
         <v>16.7</v>
       </c>
       <c r="M12">
-        <v>0.4864512999999999</v>
+        <v>0.53509643</v>
       </c>
       <c r="N12">
-        <v>16.2135487</v>
+        <v>16.16490357</v>
       </c>
       <c r="O12">
-        <v>3.566980714</v>
+        <v>3.5562787854</v>
       </c>
       <c r="P12">
-        <v>12.646567986</v>
+        <v>12.6086247846</v>
       </c>
       <c r="Q12">
-        <v>15.146567986</v>
+        <v>15.1086247846</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.11896945461405</v>
+        <v>0.1196251400831219</v>
       </c>
       <c r="T12">
-        <v>1.064704718903333</v>
+        <v>1.074245741406775</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.33026080925265</v>
+        <v>31.2093280084115</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1107821146739785</v>
+        <v>0.1105683201953121</v>
       </c>
       <c r="C13">
-        <v>88.53566585222974</v>
+        <v>87.80275329241303</v>
       </c>
       <c r="D13">
-        <v>83.07376585222973</v>
+        <v>83.30795329241303</v>
       </c>
       <c r="E13">
-        <v>7.428099999999999</v>
+        <v>8.395199999999997</v>
       </c>
       <c r="F13">
-        <v>10.6381</v>
+        <v>11.6052</v>
       </c>
       <c r="G13">
         <v>16.1</v>
@@ -2609,28 +2609,28 @@
         <v>16.7</v>
       </c>
       <c r="M13">
-        <v>0.53509643</v>
+        <v>0.5837415599999999</v>
       </c>
       <c r="N13">
-        <v>16.16490357</v>
+        <v>16.11625844</v>
       </c>
       <c r="O13">
-        <v>3.5562787854</v>
+        <v>3.5455768568</v>
       </c>
       <c r="P13">
-        <v>12.6086247846</v>
+        <v>12.5706815832</v>
       </c>
       <c r="Q13">
-        <v>15.1086247846</v>
+        <v>15.0706815832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1196251400831219</v>
+        <v>0.1202957274946728</v>
       </c>
       <c r="T13">
-        <v>1.074245741406775</v>
+        <v>1.08400360533075</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.2093280084115</v>
+        <v>28.60855067437721</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1105683201953121</v>
+        <v>0.1103545257166456</v>
       </c>
       <c r="C14">
-        <v>87.80275329241303</v>
+        <v>87.07116482811183</v>
       </c>
       <c r="D14">
-        <v>83.30795329241303</v>
+        <v>83.54346482811184</v>
       </c>
       <c r="E14">
-        <v>8.395199999999997</v>
+        <v>9.362299999999999</v>
       </c>
       <c r="F14">
-        <v>11.6052</v>
+        <v>12.5723</v>
       </c>
       <c r="G14">
         <v>16.1</v>
@@ -2691,28 +2691,28 @@
         <v>16.7</v>
       </c>
       <c r="M14">
-        <v>0.5837415599999999</v>
+        <v>0.63238669</v>
       </c>
       <c r="N14">
-        <v>16.11625844</v>
+        <v>16.06761331</v>
       </c>
       <c r="O14">
-        <v>3.5455768568</v>
+        <v>3.5348749282</v>
       </c>
       <c r="P14">
-        <v>12.5706815832</v>
+        <v>12.5327383818</v>
       </c>
       <c r="Q14">
-        <v>15.0706815832</v>
+        <v>15.0327383818</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1202957274946728</v>
+        <v>0.120981730708788</v>
       </c>
       <c r="T14">
-        <v>1.08400360533075</v>
+        <v>1.093985787965621</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.60855067437721</v>
+        <v>26.40789293019434</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1103545257166456</v>
+        <v>0.1101407312379791</v>
       </c>
       <c r="C15">
-        <v>87.07116482811183</v>
+        <v>86.34091172081406</v>
       </c>
       <c r="D15">
-        <v>83.54346482811184</v>
+        <v>83.78031172081405</v>
       </c>
       <c r="E15">
-        <v>9.362299999999999</v>
+        <v>10.3294</v>
       </c>
       <c r="F15">
-        <v>12.5723</v>
+        <v>13.5394</v>
       </c>
       <c r="G15">
         <v>16.1</v>
@@ -2773,28 +2773,28 @@
         <v>16.7</v>
       </c>
       <c r="M15">
-        <v>0.63238669</v>
+        <v>0.68103182</v>
       </c>
       <c r="N15">
-        <v>16.06761331</v>
+        <v>16.01896818</v>
       </c>
       <c r="O15">
-        <v>3.5348749282</v>
+        <v>3.5241729996</v>
       </c>
       <c r="P15">
-        <v>12.5327383818</v>
+        <v>12.4947951804</v>
       </c>
       <c r="Q15">
-        <v>15.0327383818</v>
+        <v>14.9947951804</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.120981730708788</v>
+        <v>0.1216836874860222</v>
       </c>
       <c r="T15">
-        <v>1.093985787965621</v>
+        <v>1.104200114382698</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.40789293019434</v>
+        <v>24.52161486375189</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1101407312379791</v>
+        <v>0.1099269367593126</v>
       </c>
       <c r="C16">
-        <v>86.34091172081406</v>
+        <v>85.61200536007674</v>
       </c>
       <c r="D16">
-        <v>83.78031172081405</v>
+        <v>84.01850536007674</v>
       </c>
       <c r="E16">
-        <v>10.3294</v>
+        <v>11.2965</v>
       </c>
       <c r="F16">
-        <v>13.5394</v>
+        <v>14.5065</v>
       </c>
       <c r="G16">
         <v>16.1</v>
@@ -2855,28 +2855,28 @@
         <v>16.7</v>
       </c>
       <c r="M16">
-        <v>0.68103182</v>
+        <v>0.72967695</v>
       </c>
       <c r="N16">
-        <v>16.01896818</v>
+        <v>15.97032305</v>
       </c>
       <c r="O16">
-        <v>3.5241729996</v>
+        <v>3.513471071</v>
       </c>
       <c r="P16">
-        <v>12.4947951804</v>
+        <v>12.456851979</v>
       </c>
       <c r="Q16">
-        <v>14.9947951804</v>
+        <v>14.956851979</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1216836874860222</v>
+        <v>0.1224021608933089</v>
       </c>
       <c r="T16">
-        <v>1.104200114382698</v>
+        <v>1.114654777891942</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.52161486375189</v>
+        <v>22.88684053950176</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1099269367593126</v>
+        <v>0.1097131422806461</v>
       </c>
       <c r="C17">
-        <v>85.61200536007674</v>
+        <v>84.88445726535156</v>
       </c>
       <c r="D17">
-        <v>84.01850536007674</v>
+        <v>84.25805726535155</v>
       </c>
       <c r="E17">
-        <v>11.2965</v>
+        <v>12.2636</v>
       </c>
       <c r="F17">
-        <v>14.5065</v>
+        <v>15.4736</v>
       </c>
       <c r="G17">
         <v>16.1</v>
@@ -2937,28 +2937,28 @@
         <v>16.7</v>
       </c>
       <c r="M17">
-        <v>0.7296769499999999</v>
+        <v>0.7783220799999999</v>
       </c>
       <c r="N17">
-        <v>15.97032305</v>
+        <v>15.92167792</v>
       </c>
       <c r="O17">
-        <v>3.513471071</v>
+        <v>3.5027691424</v>
       </c>
       <c r="P17">
-        <v>12.456851979</v>
+        <v>12.4189087776</v>
       </c>
       <c r="Q17">
-        <v>14.956851979</v>
+        <v>14.9189087776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1224021608933089</v>
+        <v>0.123137740810293</v>
       </c>
       <c r="T17">
-        <v>1.114654777891942</v>
+        <v>1.125358361960929</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.88684053950177</v>
+        <v>21.4564130057829</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1097131422806461</v>
+        <v>0.1094993478019796</v>
       </c>
       <c r="C18">
-        <v>84.88445726535156</v>
+        <v>84.15827908784192</v>
       </c>
       <c r="D18">
-        <v>84.25805726535155</v>
+        <v>84.4989790878419</v>
       </c>
       <c r="E18">
-        <v>12.2636</v>
+        <v>13.2307</v>
       </c>
       <c r="F18">
-        <v>15.4736</v>
+        <v>16.4407</v>
       </c>
       <c r="G18">
         <v>16.1</v>
@@ -3019,28 +3019,28 @@
         <v>16.7</v>
       </c>
       <c r="M18">
-        <v>0.7783220799999999</v>
+        <v>0.82696721</v>
       </c>
       <c r="N18">
-        <v>15.92167792</v>
+        <v>15.87303279</v>
       </c>
       <c r="O18">
-        <v>3.5027691424</v>
+        <v>3.4920672138</v>
       </c>
       <c r="P18">
-        <v>12.4189087776</v>
+        <v>12.3809655762</v>
       </c>
       <c r="Q18">
-        <v>14.9189087776</v>
+        <v>14.8809655762</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.123137740810293</v>
+        <v>0.1238910455445538</v>
       </c>
       <c r="T18">
-        <v>1.125358361960929</v>
+        <v>1.136319863718326</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.4564130057829</v>
+        <v>20.19427106426626</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1094993478019796</v>
+        <v>0.1092855533233132</v>
       </c>
       <c r="C19">
-        <v>84.15827908784192</v>
+        <v>83.43348261239211</v>
       </c>
       <c r="D19">
-        <v>84.4989790878419</v>
+        <v>84.74128261239213</v>
       </c>
       <c r="E19">
-        <v>13.2307</v>
+        <v>14.1978</v>
       </c>
       <c r="F19">
-        <v>16.4407</v>
+        <v>17.4078</v>
       </c>
       <c r="G19">
         <v>16.1</v>
@@ -3101,28 +3101,28 @@
         <v>16.7</v>
       </c>
       <c r="M19">
-        <v>0.82696721</v>
+        <v>0.87561234</v>
       </c>
       <c r="N19">
-        <v>15.87303279</v>
+        <v>15.82438766</v>
       </c>
       <c r="O19">
-        <v>3.4920672138</v>
+        <v>3.4813652852</v>
       </c>
       <c r="P19">
-        <v>12.3809655762</v>
+        <v>12.3430223748</v>
       </c>
       <c r="Q19">
-        <v>14.8809655762</v>
+        <v>14.8430223748</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1238910455445538</v>
+        <v>0.1246627235650161</v>
       </c>
       <c r="T19">
-        <v>1.136319863718326</v>
+        <v>1.147548719177123</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.19427106426626</v>
+        <v>19.07236711625147</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1092855533233132</v>
+        <v>0.1090717588446467</v>
       </c>
       <c r="C20">
-        <v>83.43348261239215</v>
+        <v>82.7100797594089</v>
       </c>
       <c r="D20">
-        <v>84.74128261239214</v>
+        <v>84.98497975940889</v>
       </c>
       <c r="E20">
-        <v>14.1978</v>
+        <v>15.1649</v>
       </c>
       <c r="F20">
-        <v>17.4078</v>
+        <v>18.3749</v>
       </c>
       <c r="G20">
         <v>16.1</v>
@@ -3183,28 +3183,28 @@
         <v>16.7</v>
       </c>
       <c r="M20">
-        <v>0.8756123399999999</v>
+        <v>0.9242574699999999</v>
       </c>
       <c r="N20">
-        <v>15.82438766</v>
+        <v>15.77574253</v>
       </c>
       <c r="O20">
-        <v>3.4813652852</v>
+        <v>3.4706633566</v>
       </c>
       <c r="P20">
-        <v>12.3430223748</v>
+        <v>12.3050791734</v>
       </c>
       <c r="Q20">
-        <v>14.8430223748</v>
+        <v>14.8050791734</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.124662723565016</v>
+        <v>0.1254534553637613</v>
       </c>
       <c r="T20">
-        <v>1.147548719177123</v>
+        <v>1.15905483032626</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.07236711625147</v>
+        <v>18.06855832065929</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1090717588446467</v>
+        <v>0.1088579643659802</v>
       </c>
       <c r="C21">
-        <v>82.7100797594089</v>
+        <v>81.98808258681611</v>
       </c>
       <c r="D21">
-        <v>84.98497975940889</v>
+        <v>85.2300825868161</v>
       </c>
       <c r="E21">
-        <v>15.1649</v>
+        <v>16.132</v>
       </c>
       <c r="F21">
-        <v>18.3749</v>
+        <v>19.342</v>
       </c>
       <c r="G21">
         <v>16.1</v>
@@ -3265,28 +3265,28 @@
         <v>16.7</v>
       </c>
       <c r="M21">
-        <v>0.9242574699999999</v>
+        <v>0.9729025999999998</v>
       </c>
       <c r="N21">
-        <v>15.77574253</v>
+        <v>15.7270974</v>
       </c>
       <c r="O21">
-        <v>3.4706633566</v>
+        <v>3.459961428</v>
       </c>
       <c r="P21">
-        <v>12.3050791734</v>
+        <v>12.267135972</v>
       </c>
       <c r="Q21">
-        <v>14.8050791734</v>
+        <v>14.767135972</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1254534553637613</v>
+        <v>0.1262639554574752</v>
       </c>
       <c r="T21">
-        <v>1.15905483032626</v>
+        <v>1.170848594254126</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.06855832065929</v>
+        <v>17.16513040462632</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1088579643659802</v>
+        <v>0.1086441698873137</v>
       </c>
       <c r="C22">
-        <v>81.98808258681611</v>
+        <v>81.26750329204367</v>
       </c>
       <c r="D22">
-        <v>85.2300825868161</v>
+        <v>85.47660329204366</v>
       </c>
       <c r="E22">
-        <v>16.132</v>
+        <v>17.0991</v>
       </c>
       <c r="F22">
-        <v>19.342</v>
+        <v>20.3091</v>
       </c>
       <c r="G22">
         <v>16.1</v>
@@ -3347,28 +3347,28 @@
         <v>16.7</v>
       </c>
       <c r="M22">
-        <v>0.9729025999999998</v>
+        <v>1.02154773</v>
       </c>
       <c r="N22">
-        <v>15.7270974</v>
+        <v>15.67845227</v>
       </c>
       <c r="O22">
-        <v>3.459961428</v>
+        <v>3.4492594994</v>
       </c>
       <c r="P22">
-        <v>12.267135972</v>
+        <v>12.2291927706</v>
       </c>
       <c r="Q22">
-        <v>14.767135972</v>
+        <v>14.7291927706</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1262639554574752</v>
+        <v>0.1270949745409034</v>
       </c>
       <c r="T22">
-        <v>1.170848594254126</v>
+        <v>1.182940934483963</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.16513040462632</v>
+        <v>16.34774324250126</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1086441698873137</v>
+        <v>0.1084303754086473</v>
       </c>
       <c r="C23">
-        <v>81.26750329204367</v>
+        <v>80.54835421405109</v>
       </c>
       <c r="D23">
-        <v>85.47660329204368</v>
+        <v>85.72455421405108</v>
       </c>
       <c r="E23">
-        <v>17.0991</v>
+        <v>18.0662</v>
       </c>
       <c r="F23">
-        <v>20.3091</v>
+        <v>21.2762</v>
       </c>
       <c r="G23">
         <v>16.1</v>
@@ -3429,28 +3429,28 @@
         <v>16.7</v>
       </c>
       <c r="M23">
-        <v>1.02154773</v>
+        <v>1.07019286</v>
       </c>
       <c r="N23">
-        <v>15.67845227</v>
+        <v>15.62980714</v>
       </c>
       <c r="O23">
-        <v>3.4492594994</v>
+        <v>3.4385575708</v>
       </c>
       <c r="P23">
-        <v>12.2291927706</v>
+        <v>12.1912495692</v>
       </c>
       <c r="Q23">
-        <v>14.7291927706</v>
+        <v>14.6912495692</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1270949745409034</v>
+        <v>0.127947301805958</v>
       </c>
       <c r="T23">
-        <v>1.182940934483963</v>
+        <v>1.195343334719693</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.34774324250126</v>
+        <v>15.60466400420575</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1084303754086473</v>
+        <v>0.1082165809299808</v>
       </c>
       <c r="C24">
-        <v>80.54835421405109</v>
+        <v>79.83064783538586</v>
       </c>
       <c r="D24">
-        <v>85.72455421405108</v>
+        <v>85.97394783538587</v>
       </c>
       <c r="E24">
-        <v>18.0662</v>
+        <v>19.0333</v>
       </c>
       <c r="F24">
-        <v>21.2762</v>
+        <v>22.2433</v>
       </c>
       <c r="G24">
         <v>16.1</v>
@@ -3511,28 +3511,28 @@
         <v>16.7</v>
       </c>
       <c r="M24">
-        <v>1.07019286</v>
+        <v>1.11883799</v>
       </c>
       <c r="N24">
-        <v>15.62980714</v>
+        <v>15.58116201</v>
       </c>
       <c r="O24">
-        <v>3.4385575708</v>
+        <v>3.4278556422</v>
       </c>
       <c r="P24">
-        <v>12.1912495692</v>
+        <v>12.1533063678</v>
       </c>
       <c r="Q24">
-        <v>14.6912495692</v>
+        <v>14.6533063678</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.127947301805958</v>
+        <v>0.1288217674415335</v>
       </c>
       <c r="T24">
-        <v>1.195343334719693</v>
+        <v>1.208067875221287</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.60466400420575</v>
+        <v>14.92620035184898</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1082165809299808</v>
+        <v>0.1080027864513143</v>
       </c>
       <c r="C25">
-        <v>79.83064783538586</v>
+        <v>79.1143967842786</v>
       </c>
       <c r="D25">
-        <v>85.97394783538587</v>
+        <v>86.2247967842786</v>
       </c>
       <c r="E25">
-        <v>19.0333</v>
+        <v>20.0004</v>
       </c>
       <c r="F25">
-        <v>22.2433</v>
+        <v>23.2104</v>
       </c>
       <c r="G25">
         <v>16.1</v>
@@ -3593,28 +3593,28 @@
         <v>16.7</v>
       </c>
       <c r="M25">
-        <v>1.11883799</v>
+        <v>1.16748312</v>
       </c>
       <c r="N25">
-        <v>15.58116201</v>
+        <v>15.53251688</v>
       </c>
       <c r="O25">
-        <v>3.4278556422</v>
+        <v>3.4171537136</v>
       </c>
       <c r="P25">
-        <v>12.1533063678</v>
+        <v>12.1153631664</v>
       </c>
       <c r="Q25">
-        <v>14.6533063678</v>
+        <v>14.6153631664</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1288217674415335</v>
+        <v>0.1297192453306767</v>
       </c>
       <c r="T25">
-        <v>1.208067875221287</v>
+        <v>1.22112727205187</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.92620035184898</v>
+        <v>14.3042753371886</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1080027864513143</v>
+        <v>0.1077889919726478</v>
       </c>
       <c r="C26">
-        <v>79.1143967842786</v>
+        <v>78.39961383677409</v>
       </c>
       <c r="D26">
-        <v>86.2247967842786</v>
+        <v>86.47711383677409</v>
       </c>
       <c r="E26">
-        <v>20.0004</v>
+        <v>20.9675</v>
       </c>
       <c r="F26">
-        <v>23.2104</v>
+        <v>24.1775</v>
       </c>
       <c r="G26">
         <v>16.1</v>
@@ -3675,28 +3675,28 @@
         <v>16.7</v>
       </c>
       <c r="M26">
-        <v>1.16748312</v>
+        <v>1.21612825</v>
       </c>
       <c r="N26">
-        <v>15.53251688</v>
+        <v>15.48387175</v>
       </c>
       <c r="O26">
-        <v>3.4171537136</v>
+        <v>3.406451785</v>
       </c>
       <c r="P26">
-        <v>12.1153631664</v>
+        <v>12.077419965</v>
       </c>
       <c r="Q26">
-        <v>14.6153631664</v>
+        <v>14.577419965</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1297192453306767</v>
+        <v>0.1306406559635304</v>
       </c>
       <c r="T26">
-        <v>1.22112727205187</v>
+        <v>1.234534919464601</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.3042753371886</v>
+        <v>13.73210432370106</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1077889919726478</v>
+        <v>0.1075751974939813</v>
       </c>
       <c r="C27">
-        <v>78.39961383677409</v>
+        <v>77.68631191890091</v>
       </c>
       <c r="D27">
-        <v>86.47711383677409</v>
+        <v>86.73091191890092</v>
       </c>
       <c r="E27">
-        <v>20.9675</v>
+        <v>21.9346</v>
       </c>
       <c r="F27">
-        <v>24.1775</v>
+        <v>25.1446</v>
       </c>
       <c r="G27">
         <v>16.1</v>
@@ -3757,28 +3757,28 @@
         <v>16.7</v>
       </c>
       <c r="M27">
-        <v>1.21612825</v>
+        <v>1.26477338</v>
       </c>
       <c r="N27">
-        <v>15.48387175</v>
+        <v>15.43522662</v>
       </c>
       <c r="O27">
-        <v>3.406451785</v>
+        <v>3.3957498564</v>
       </c>
       <c r="P27">
-        <v>12.077419965</v>
+        <v>12.0394767636</v>
       </c>
       <c r="Q27">
-        <v>14.577419965</v>
+        <v>14.5394767636</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1306406559635304</v>
+        <v>0.1315869695864612</v>
       </c>
       <c r="T27">
-        <v>1.234534919464601</v>
+        <v>1.248304935726326</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.73210432370106</v>
+        <v>13.20394646509717</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1075751974939813</v>
+        <v>0.1076773030153148</v>
       </c>
       <c r="C28">
-        <v>77.68631191890091</v>
+        <v>76.59781560474396</v>
       </c>
       <c r="D28">
-        <v>86.73091191890092</v>
+        <v>86.60951560474395</v>
       </c>
       <c r="E28">
-        <v>21.9346</v>
+        <v>22.9017</v>
       </c>
       <c r="F28">
-        <v>25.1446</v>
+        <v>26.1117</v>
       </c>
       <c r="G28">
         <v>16.1</v>
@@ -3839,45 +3839,45 @@
         <v>16.7</v>
       </c>
       <c r="M28">
-        <v>1.26477338</v>
+        <v>1.35258606</v>
       </c>
       <c r="N28">
-        <v>15.43522662</v>
+        <v>15.34741394</v>
       </c>
       <c r="O28">
-        <v>3.3957498564</v>
+        <v>3.3764310668</v>
       </c>
       <c r="P28">
-        <v>12.0394767636</v>
+        <v>11.9709828732</v>
       </c>
       <c r="Q28">
-        <v>14.5394767636</v>
+        <v>14.4709828732</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1315869695864612</v>
+        <v>0.1325592096100203</v>
       </c>
       <c r="T28">
-        <v>1.248304935726326</v>
+        <v>1.262452212707549</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.20394646509717</v>
+        <v>12.34671899546266</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1076773030153148</v>
+        <v>0.1074752085366483</v>
       </c>
       <c r="C29">
-        <v>76.59781560474396</v>
+        <v>75.87132204210391</v>
       </c>
       <c r="D29">
-        <v>86.60951560474395</v>
+        <v>86.85012204210392</v>
       </c>
       <c r="E29">
-        <v>22.9017</v>
+        <v>23.8688</v>
       </c>
       <c r="F29">
-        <v>26.1117</v>
+        <v>27.0788</v>
       </c>
       <c r="G29">
         <v>16.1</v>
@@ -3921,28 +3921,28 @@
         <v>16.7</v>
       </c>
       <c r="M29">
-        <v>1.35258606</v>
+        <v>1.40268184</v>
       </c>
       <c r="N29">
-        <v>15.34741394</v>
+        <v>15.29731816</v>
       </c>
       <c r="O29">
-        <v>3.3764310668</v>
+        <v>3.3654099952</v>
       </c>
       <c r="P29">
-        <v>11.9709828732</v>
+        <v>11.9319081648</v>
       </c>
       <c r="Q29">
-        <v>14.4709828732</v>
+        <v>14.4319081648</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1325592096100203</v>
+        <v>0.1335584563009005</v>
       </c>
       <c r="T29">
-        <v>1.262452212707549</v>
+        <v>1.276992469604918</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.34671899546266</v>
+        <v>11.90576474562471</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1074752085366483</v>
+        <v>0.1072731140579819</v>
       </c>
       <c r="C30">
-        <v>75.87132204210391</v>
+        <v>75.14616904190139</v>
       </c>
       <c r="D30">
-        <v>86.85012204210392</v>
+        <v>87.09206904190138</v>
       </c>
       <c r="E30">
-        <v>23.8688</v>
+        <v>24.8359</v>
       </c>
       <c r="F30">
-        <v>27.0788</v>
+        <v>28.0459</v>
       </c>
       <c r="G30">
         <v>16.1</v>
@@ -4003,28 +4003,28 @@
         <v>16.7</v>
       </c>
       <c r="M30">
-        <v>1.40268184</v>
+        <v>1.45277762</v>
       </c>
       <c r="N30">
-        <v>15.29731816</v>
+        <v>15.24722238</v>
       </c>
       <c r="O30">
-        <v>3.3654099952</v>
+        <v>3.3543889236</v>
       </c>
       <c r="P30">
-        <v>11.9319081648</v>
+        <v>11.8928334564</v>
       </c>
       <c r="Q30">
-        <v>14.4319081648</v>
+        <v>14.3928334564</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1335584563009005</v>
+        <v>0.1345858507858899</v>
       </c>
       <c r="T30">
-        <v>1.276992469604918</v>
+        <v>1.291942311203621</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.90576474562471</v>
+        <v>11.49522113370661</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1072731140579819</v>
+        <v>0.1070710195793154</v>
       </c>
       <c r="C31">
-        <v>75.1461690419014</v>
+        <v>74.42236783904781</v>
       </c>
       <c r="D31">
-        <v>87.09206904190138</v>
+        <v>87.33536783904781</v>
       </c>
       <c r="E31">
-        <v>24.8359</v>
+        <v>25.803</v>
       </c>
       <c r="F31">
-        <v>28.0459</v>
+        <v>29.013</v>
       </c>
       <c r="G31">
         <v>16.1</v>
@@ -4085,28 +4085,28 @@
         <v>16.7</v>
       </c>
       <c r="M31">
-        <v>1.45277762</v>
+        <v>1.5028734</v>
       </c>
       <c r="N31">
-        <v>15.24722238</v>
+        <v>15.1971266</v>
       </c>
       <c r="O31">
-        <v>3.3543889236</v>
+        <v>3.343367852</v>
       </c>
       <c r="P31">
-        <v>11.8928334564</v>
+        <v>11.853758748</v>
       </c>
       <c r="Q31">
-        <v>14.3928334564</v>
+        <v>14.353758748</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1345858507858899</v>
+        <v>0.135642599399022</v>
       </c>
       <c r="T31">
-        <v>1.291942311203621</v>
+        <v>1.307319291133716</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.49522113370662</v>
+        <v>11.1120470959164</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1070710195793154</v>
+        <v>0.1068689251006489</v>
       </c>
       <c r="C32">
-        <v>74.42236783904781</v>
+        <v>73.699929794349</v>
       </c>
       <c r="D32">
-        <v>87.33536783904781</v>
+        <v>87.58002979434899</v>
       </c>
       <c r="E32">
-        <v>25.803</v>
+        <v>26.7701</v>
       </c>
       <c r="F32">
-        <v>29.013</v>
+        <v>29.9801</v>
       </c>
       <c r="G32">
         <v>16.1</v>
@@ -4167,28 +4167,28 @@
         <v>16.7</v>
       </c>
       <c r="M32">
-        <v>1.5028734</v>
+        <v>1.55296918</v>
       </c>
       <c r="N32">
-        <v>15.1971266</v>
+        <v>15.14703082</v>
       </c>
       <c r="O32">
-        <v>3.343367852</v>
+        <v>3.3323467804</v>
       </c>
       <c r="P32">
-        <v>11.853758748</v>
+        <v>11.8146840396</v>
       </c>
       <c r="Q32">
-        <v>14.353758748</v>
+        <v>14.3146840396</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.135642599399022</v>
+        <v>0.1367299784067375</v>
       </c>
       <c r="T32">
-        <v>1.307319291133716</v>
+        <v>1.323141980627002</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.1120470959164</v>
+        <v>10.75359396379006</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1068689251006489</v>
+        <v>0.1066668306219824</v>
       </c>
       <c r="C33">
-        <v>73.699929794349</v>
+        <v>72.97886639627318</v>
       </c>
       <c r="D33">
-        <v>87.58002979434899</v>
+        <v>87.82606639627316</v>
       </c>
       <c r="E33">
-        <v>26.7701</v>
+        <v>27.7372</v>
       </c>
       <c r="F33">
-        <v>29.9801</v>
+        <v>30.9472</v>
       </c>
       <c r="G33">
         <v>16.1</v>
@@ -4249,28 +4249,28 @@
         <v>16.7</v>
       </c>
       <c r="M33">
-        <v>1.55296918</v>
+        <v>1.60306496</v>
       </c>
       <c r="N33">
-        <v>15.14703082</v>
+        <v>15.09693504</v>
       </c>
       <c r="O33">
-        <v>3.3323467804</v>
+        <v>3.3213257088</v>
       </c>
       <c r="P33">
-        <v>11.8146840396</v>
+        <v>11.7756093312</v>
       </c>
       <c r="Q33">
-        <v>14.3146840396</v>
+        <v>14.2756093312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1367299784067375</v>
+        <v>0.1378493391499742</v>
       </c>
       <c r="T33">
-        <v>1.323141980627002</v>
+        <v>1.339430043340679</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.75359396379006</v>
+        <v>10.41754415242162</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1066668306219824</v>
+        <v>0.1064647361433159</v>
       </c>
       <c r="C34">
-        <v>72.97886639627318</v>
+        <v>72.25918926274971</v>
       </c>
       <c r="D34">
-        <v>87.82606639627316</v>
+        <v>88.0734892627497</v>
       </c>
       <c r="E34">
-        <v>27.7372</v>
+        <v>28.7043</v>
       </c>
       <c r="F34">
-        <v>30.9472</v>
+        <v>31.9143</v>
       </c>
       <c r="G34">
         <v>16.1</v>
@@ -4331,28 +4331,28 @@
         <v>16.7</v>
       </c>
       <c r="M34">
-        <v>1.60306496</v>
+        <v>1.65316074</v>
       </c>
       <c r="N34">
-        <v>15.09693504</v>
+        <v>15.04683926</v>
       </c>
       <c r="O34">
-        <v>3.3213257088</v>
+        <v>3.3103046372</v>
       </c>
       <c r="P34">
-        <v>11.7756093312</v>
+        <v>11.7365346228</v>
       </c>
       <c r="Q34">
-        <v>14.2756093312</v>
+        <v>14.2365346228</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1378493391499742</v>
+        <v>0.1390021136467402</v>
       </c>
       <c r="T34">
-        <v>1.339430043340679</v>
+        <v>1.356204316881629</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.41754415242162</v>
+        <v>10.10186099628763</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1064647361433159</v>
+        <v>0.1067134816646494</v>
       </c>
       <c r="C35">
-        <v>72.25918926274971</v>
+        <v>70.98774920946353</v>
       </c>
       <c r="D35">
-        <v>88.0734892627497</v>
+        <v>87.76914920946354</v>
       </c>
       <c r="E35">
-        <v>28.7043</v>
+        <v>29.6714</v>
       </c>
       <c r="F35">
-        <v>31.9143</v>
+        <v>32.8814</v>
       </c>
       <c r="G35">
         <v>16.1</v>
@@ -4413,45 +4413,45 @@
         <v>16.7</v>
       </c>
       <c r="M35">
-        <v>1.65316074</v>
+        <v>1.7591549</v>
       </c>
       <c r="N35">
-        <v>15.04683926</v>
+        <v>14.9408451</v>
       </c>
       <c r="O35">
-        <v>3.3103046372</v>
+        <v>3.286985922</v>
       </c>
       <c r="P35">
-        <v>11.7365346228</v>
+        <v>11.653859178</v>
       </c>
       <c r="Q35">
-        <v>14.2365346228</v>
+        <v>14.153859178</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1390021136467402</v>
+        <v>0.1401898207040143</v>
       </c>
       <c r="T35">
-        <v>1.356204316881629</v>
+        <v>1.373486901742002</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>10.10186099628763</v>
+        <v>9.493194715257877</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1067134816646494</v>
+        <v>0.106524647185983</v>
       </c>
       <c r="C36">
-        <v>70.98774920946353</v>
+        <v>70.25149533115285</v>
       </c>
       <c r="D36">
-        <v>87.76914920946354</v>
+        <v>87.99999533115285</v>
       </c>
       <c r="E36">
-        <v>29.6714</v>
+        <v>30.6385</v>
       </c>
       <c r="F36">
-        <v>32.8814</v>
+        <v>33.8485</v>
       </c>
       <c r="G36">
         <v>16.1</v>
@@ -4495,28 +4495,28 @@
         <v>16.7</v>
       </c>
       <c r="M36">
-        <v>1.7591549</v>
+        <v>1.81089475</v>
       </c>
       <c r="N36">
-        <v>14.9408451</v>
+        <v>14.88910525</v>
       </c>
       <c r="O36">
-        <v>3.286985922</v>
+        <v>3.275603155</v>
       </c>
       <c r="P36">
-        <v>11.653859178</v>
+        <v>11.613502095</v>
       </c>
       <c r="Q36">
-        <v>14.153859178</v>
+        <v>14.113502095</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1401898207040143</v>
+        <v>0.14141407259382</v>
       </c>
       <c r="T36">
-        <v>1.373486901742002</v>
+        <v>1.391301258444233</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.493194715257877</v>
+        <v>9.221960580536223</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.106524647185983</v>
+        <v>0.1063358127073165</v>
       </c>
       <c r="C37">
-        <v>70.25149533115285</v>
+        <v>69.51645897545841</v>
       </c>
       <c r="D37">
-        <v>87.99999533115285</v>
+        <v>88.23205897545841</v>
       </c>
       <c r="E37">
-        <v>30.6385</v>
+        <v>31.6056</v>
       </c>
       <c r="F37">
-        <v>33.8485</v>
+        <v>34.8156</v>
       </c>
       <c r="G37">
         <v>16.1</v>
@@ -4577,28 +4577,28 @@
         <v>16.7</v>
       </c>
       <c r="M37">
-        <v>1.81089475</v>
+        <v>1.8626346</v>
       </c>
       <c r="N37">
-        <v>14.88910525</v>
+        <v>14.8373654</v>
       </c>
       <c r="O37">
-        <v>3.275603155</v>
+        <v>3.264220388</v>
       </c>
       <c r="P37">
-        <v>11.613502095</v>
+        <v>11.573145012</v>
       </c>
       <c r="Q37">
-        <v>14.113502095</v>
+        <v>14.073145012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.14141407259382</v>
+        <v>0.142676582355182</v>
       </c>
       <c r="T37">
-        <v>1.391301258444233</v>
+        <v>1.409672313793409</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.221960580536223</v>
+        <v>8.965795008854661</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1063358127073165</v>
+        <v>0.10614697822865</v>
       </c>
       <c r="C38">
-        <v>69.51645897545842</v>
+        <v>68.78264979998744</v>
       </c>
       <c r="D38">
-        <v>88.23205897545841</v>
+        <v>88.46534979998744</v>
       </c>
       <c r="E38">
-        <v>31.6056</v>
+        <v>32.5727</v>
       </c>
       <c r="F38">
-        <v>34.8156</v>
+        <v>35.7827</v>
       </c>
       <c r="G38">
         <v>16.1</v>
@@ -4659,28 +4659,28 @@
         <v>16.7</v>
       </c>
       <c r="M38">
-        <v>1.8626346</v>
+        <v>1.91437445</v>
       </c>
       <c r="N38">
-        <v>14.8373654</v>
+        <v>14.78562555</v>
       </c>
       <c r="O38">
-        <v>3.264220388</v>
+        <v>3.252837621</v>
       </c>
       <c r="P38">
-        <v>11.573145012</v>
+        <v>11.532787929</v>
       </c>
       <c r="Q38">
-        <v>14.073145012</v>
+        <v>14.032787929</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.142676582355182</v>
+        <v>0.143979171791508</v>
       </c>
       <c r="T38">
-        <v>1.409672313793409</v>
+        <v>1.428626577248908</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.965795008854663</v>
+        <v>8.723476224831563</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.10614697822865</v>
+        <v>0.1059581437499835</v>
       </c>
       <c r="C39">
-        <v>68.78264979998744</v>
+        <v>68.05007756475899</v>
       </c>
       <c r="D39">
-        <v>88.46534979998744</v>
+        <v>88.69987756475898</v>
       </c>
       <c r="E39">
-        <v>32.5727</v>
+        <v>33.5398</v>
       </c>
       <c r="F39">
-        <v>35.7827</v>
+        <v>36.7498</v>
       </c>
       <c r="G39">
         <v>16.1</v>
@@ -4741,28 +4741,28 @@
         <v>16.7</v>
       </c>
       <c r="M39">
-        <v>1.91437445</v>
+        <v>1.9661143</v>
       </c>
       <c r="N39">
-        <v>14.78562555</v>
+        <v>14.7338857</v>
       </c>
       <c r="O39">
-        <v>3.252837621</v>
+        <v>3.241454854</v>
       </c>
       <c r="P39">
-        <v>11.532787929</v>
+        <v>11.492430846</v>
       </c>
       <c r="Q39">
-        <v>14.032787929</v>
+        <v>13.992430846</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.143979171791508</v>
+        <v>0.1453237802419089</v>
       </c>
       <c r="T39">
-        <v>1.428626577248908</v>
+        <v>1.448192268557809</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.723476224831563</v>
+        <v>8.493911061020205</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1059581437499835</v>
+        <v>0.1057693092713171</v>
       </c>
       <c r="C40">
-        <v>68.05007756475899</v>
+        <v>67.31875213356518</v>
       </c>
       <c r="D40">
-        <v>88.69987756475898</v>
+        <v>88.93565213356518</v>
       </c>
       <c r="E40">
-        <v>33.5398</v>
+        <v>34.50689999999999</v>
       </c>
       <c r="F40">
-        <v>36.7498</v>
+        <v>37.7169</v>
       </c>
       <c r="G40">
         <v>16.1</v>
@@ -4823,28 +4823,28 @@
         <v>16.7</v>
       </c>
       <c r="M40">
-        <v>1.9661143</v>
+        <v>2.01785415</v>
       </c>
       <c r="N40">
-        <v>14.7338857</v>
+        <v>14.68214585</v>
       </c>
       <c r="O40">
-        <v>3.241454854</v>
+        <v>3.230072087</v>
       </c>
       <c r="P40">
-        <v>11.492430846</v>
+        <v>11.452073763</v>
       </c>
       <c r="Q40">
-        <v>13.992430846</v>
+        <v>13.952073763</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1453237802419089</v>
+        <v>0.1467124742152739</v>
       </c>
       <c r="T40">
-        <v>1.448192268557809</v>
+        <v>1.468399457942413</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.493911061020205</v>
+        <v>8.276118469711996</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1057693092713171</v>
+        <v>0.1055804747926506</v>
       </c>
       <c r="C41">
-        <v>67.31875213356518</v>
+        <v>66.5886834753542</v>
       </c>
       <c r="D41">
-        <v>88.93565213356518</v>
+        <v>89.17268347535421</v>
       </c>
       <c r="E41">
-        <v>34.50689999999999</v>
+        <v>35.474</v>
       </c>
       <c r="F41">
-        <v>37.7169</v>
+        <v>38.684</v>
       </c>
       <c r="G41">
         <v>16.1</v>
@@ -4905,28 +4905,28 @@
         <v>16.7</v>
       </c>
       <c r="M41">
-        <v>2.01785415</v>
+        <v>2.069594</v>
       </c>
       <c r="N41">
-        <v>14.68214585</v>
+        <v>14.630406</v>
       </c>
       <c r="O41">
-        <v>3.230072087</v>
+        <v>3.21868932</v>
       </c>
       <c r="P41">
-        <v>11.452073763</v>
+        <v>11.41171668</v>
       </c>
       <c r="Q41">
-        <v>13.952073763</v>
+        <v>13.91171668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1467124742152739</v>
+        <v>0.1481474579877509</v>
       </c>
       <c r="T41">
-        <v>1.468399457942413</v>
+        <v>1.489280220306503</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.276118469711996</v>
+        <v>8.069215507969195</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1055804747926506</v>
+        <v>0.1053916403139841</v>
       </c>
       <c r="C42">
-        <v>66.5886834753542</v>
+        <v>65.85988166563509</v>
       </c>
       <c r="D42">
-        <v>89.17268347535421</v>
+        <v>89.41098166563509</v>
       </c>
       <c r="E42">
-        <v>35.474</v>
+        <v>36.4411</v>
       </c>
       <c r="F42">
-        <v>38.684</v>
+        <v>39.6511</v>
       </c>
       <c r="G42">
         <v>16.1</v>
@@ -4987,28 +4987,28 @@
         <v>16.7</v>
       </c>
       <c r="M42">
-        <v>2.069594</v>
+        <v>2.12133385</v>
       </c>
       <c r="N42">
-        <v>14.630406</v>
+        <v>14.57866615</v>
       </c>
       <c r="O42">
-        <v>3.21868932</v>
+        <v>3.207306553</v>
       </c>
       <c r="P42">
-        <v>11.41171668</v>
+        <v>11.371359597</v>
       </c>
       <c r="Q42">
-        <v>13.91171668</v>
+        <v>13.871359597</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1481474579877509</v>
+        <v>0.1496310852779391</v>
       </c>
       <c r="T42">
-        <v>1.489280220306503</v>
+        <v>1.510868805123613</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.069215507969195</v>
+        <v>7.872405373628483</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1053916403139841</v>
+        <v>0.1052028058353176</v>
       </c>
       <c r="C43">
-        <v>65.85988166563509</v>
+        <v>65.13235688790553</v>
       </c>
       <c r="D43">
-        <v>89.41098166563509</v>
+        <v>89.65055688790554</v>
       </c>
       <c r="E43">
-        <v>36.4411</v>
+        <v>37.4082</v>
       </c>
       <c r="F43">
-        <v>39.6511</v>
+        <v>40.6182</v>
       </c>
       <c r="G43">
         <v>16.1</v>
@@ -5069,28 +5069,28 @@
         <v>16.7</v>
       </c>
       <c r="M43">
-        <v>2.12133385</v>
+        <v>2.1730737</v>
       </c>
       <c r="N43">
-        <v>14.57866615</v>
+        <v>14.5269263</v>
       </c>
       <c r="O43">
-        <v>3.207306553</v>
+        <v>3.195923786</v>
       </c>
       <c r="P43">
-        <v>11.371359597</v>
+        <v>11.331002514</v>
       </c>
       <c r="Q43">
-        <v>13.871359597</v>
+        <v>13.831002514</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1496310852779391</v>
+        <v>0.1511658721298579</v>
       </c>
       <c r="T43">
-        <v>1.510868805123613</v>
+        <v>1.533201823899935</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.872405373628483</v>
+        <v>7.684967150446853</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1052028058353176</v>
+        <v>0.1052822913566511</v>
       </c>
       <c r="C44">
-        <v>65.13235688790553</v>
+        <v>64.06425692565975</v>
       </c>
       <c r="D44">
-        <v>89.65055688790552</v>
+        <v>89.54955692565973</v>
       </c>
       <c r="E44">
-        <v>37.40819999999999</v>
+        <v>38.3753</v>
       </c>
       <c r="F44">
-        <v>40.61819999999999</v>
+        <v>41.5853</v>
       </c>
       <c r="G44">
         <v>16.1</v>
@@ -5151,45 +5151,45 @@
         <v>16.7</v>
       </c>
       <c r="M44">
-        <v>2.1730737</v>
+        <v>2.25808179</v>
       </c>
       <c r="N44">
-        <v>14.5269263</v>
+        <v>14.44191821</v>
       </c>
       <c r="O44">
-        <v>3.195923786</v>
+        <v>3.1772220062</v>
       </c>
       <c r="P44">
-        <v>11.331002514</v>
+        <v>11.2646962038</v>
       </c>
       <c r="Q44">
-        <v>13.831002514</v>
+        <v>13.7646962038</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1511658721298579</v>
+        <v>0.1527545111520195</v>
       </c>
       <c r="T44">
-        <v>1.533201823899935</v>
+        <v>1.556318457370162</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.684967150446854</v>
+        <v>7.395657709989327</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1052822913566511</v>
+        <v>0.1050996968779846</v>
       </c>
       <c r="C45">
-        <v>64.06425692565975</v>
+        <v>63.32951442585975</v>
       </c>
       <c r="D45">
-        <v>89.54955692565973</v>
+        <v>89.78191442585975</v>
       </c>
       <c r="E45">
-        <v>38.3753</v>
+        <v>39.3424</v>
       </c>
       <c r="F45">
-        <v>41.5853</v>
+        <v>42.5524</v>
       </c>
       <c r="G45">
         <v>16.1</v>
@@ -5233,28 +5233,28 @@
         <v>16.7</v>
       </c>
       <c r="M45">
-        <v>2.25808179</v>
+        <v>2.31059532</v>
       </c>
       <c r="N45">
-        <v>14.44191821</v>
+        <v>14.38940468</v>
       </c>
       <c r="O45">
-        <v>3.1772220062</v>
+        <v>3.1656690296</v>
       </c>
       <c r="P45">
-        <v>11.2646962038</v>
+        <v>11.2237356504</v>
       </c>
       <c r="Q45">
-        <v>13.7646962038</v>
+        <v>13.7237356504</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1527545111520195</v>
+        <v>0.1543998872821154</v>
       </c>
       <c r="T45">
-        <v>1.556318457370162</v>
+        <v>1.580260684892897</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.395657709989327</v>
+        <v>7.227574580216841</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1050996968779846</v>
+        <v>0.1049171023993182</v>
       </c>
       <c r="C46">
-        <v>63.32951442585975</v>
+        <v>62.59598087592044</v>
       </c>
       <c r="D46">
-        <v>89.78191442585975</v>
+        <v>90.01548087592043</v>
       </c>
       <c r="E46">
-        <v>39.3424</v>
+        <v>40.3095</v>
       </c>
       <c r="F46">
-        <v>42.5524</v>
+        <v>43.5195</v>
       </c>
       <c r="G46">
         <v>16.1</v>
@@ -5315,28 +5315,28 @@
         <v>16.7</v>
       </c>
       <c r="M46">
-        <v>2.31059532</v>
+        <v>2.36310885</v>
       </c>
       <c r="N46">
-        <v>14.38940468</v>
+        <v>14.33689115</v>
       </c>
       <c r="O46">
-        <v>3.1656690296</v>
+        <v>3.154116053</v>
       </c>
       <c r="P46">
-        <v>11.2237356504</v>
+        <v>11.182775097</v>
       </c>
       <c r="Q46">
-        <v>13.7237356504</v>
+        <v>13.682775097</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1543998872821154</v>
+        <v>0.1561050952714876</v>
       </c>
       <c r="T46">
-        <v>1.580260684892897</v>
+        <v>1.605073538871004</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.227574580216841</v>
+        <v>7.066961811767579</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1049171023993182</v>
+        <v>0.1047345079206517</v>
       </c>
       <c r="C47">
-        <v>62.59598087592044</v>
+        <v>61.86366573565199</v>
       </c>
       <c r="D47">
-        <v>90.01548087592043</v>
+        <v>90.25026573565199</v>
       </c>
       <c r="E47">
-        <v>40.3095</v>
+        <v>41.27659999999999</v>
       </c>
       <c r="F47">
-        <v>43.5195</v>
+        <v>44.4866</v>
       </c>
       <c r="G47">
         <v>16.1</v>
@@ -5397,28 +5397,28 @@
         <v>16.7</v>
       </c>
       <c r="M47">
-        <v>2.36310885</v>
+        <v>2.41562238</v>
       </c>
       <c r="N47">
-        <v>14.33689115</v>
+        <v>14.28437762</v>
       </c>
       <c r="O47">
-        <v>3.154116053</v>
+        <v>3.1425630764</v>
       </c>
       <c r="P47">
-        <v>11.182775097</v>
+        <v>11.1418145436</v>
       </c>
       <c r="Q47">
-        <v>13.682775097</v>
+        <v>13.6418145436</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1561050952714876</v>
+        <v>0.1578734591123179</v>
       </c>
       <c r="T47">
-        <v>1.605073538871004</v>
+        <v>1.630805387440893</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.066961811767579</v>
+        <v>6.913332207163936</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1047345079206517</v>
+        <v>0.1045519134419852</v>
       </c>
       <c r="C48">
-        <v>61.86366573565199</v>
+        <v>61.1325785638179</v>
       </c>
       <c r="D48">
-        <v>90.25026573565199</v>
+        <v>90.48627856381789</v>
       </c>
       <c r="E48">
-        <v>41.27659999999999</v>
+        <v>42.2437</v>
       </c>
       <c r="F48">
-        <v>44.4866</v>
+        <v>45.4537</v>
       </c>
       <c r="G48">
         <v>16.1</v>
@@ -5479,28 +5479,28 @@
         <v>16.7</v>
       </c>
       <c r="M48">
-        <v>2.41562238</v>
+        <v>2.46813591</v>
       </c>
       <c r="N48">
-        <v>14.28437762</v>
+        <v>14.23186409</v>
       </c>
       <c r="O48">
-        <v>3.1425630764</v>
+        <v>3.1310100998</v>
       </c>
       <c r="P48">
-        <v>11.1418145436</v>
+        <v>11.1008539902</v>
       </c>
       <c r="Q48">
-        <v>13.6418145436</v>
+        <v>13.6008539902</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1578734591123179</v>
+        <v>0.159708553664123</v>
       </c>
       <c r="T48">
-        <v>1.630805387440893</v>
+        <v>1.657508249164363</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.913332207163936</v>
+        <v>6.766240032543426</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1045519134419852</v>
+        <v>0.1043693189633187</v>
       </c>
       <c r="C49">
-        <v>61.1325785638179</v>
+        <v>60.40272901943185</v>
       </c>
       <c r="D49">
-        <v>90.48627856381789</v>
+        <v>90.72352901943184</v>
       </c>
       <c r="E49">
-        <v>42.2437</v>
+        <v>43.2108</v>
       </c>
       <c r="F49">
-        <v>45.4537</v>
+        <v>46.4208</v>
       </c>
       <c r="G49">
         <v>16.1</v>
@@ -5561,28 +5561,28 @@
         <v>16.7</v>
       </c>
       <c r="M49">
-        <v>2.46813591</v>
+        <v>2.52064944</v>
       </c>
       <c r="N49">
-        <v>14.23186409</v>
+        <v>14.17935056</v>
       </c>
       <c r="O49">
-        <v>3.1310100998</v>
+        <v>3.1194571232</v>
       </c>
       <c r="P49">
-        <v>11.1008539902</v>
+        <v>11.0598934368</v>
       </c>
       <c r="Q49">
-        <v>13.6008539902</v>
+        <v>13.5598934368</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.159708553664123</v>
+        <v>0.1616142287756129</v>
       </c>
       <c r="T49">
-        <v>1.657508249164363</v>
+        <v>1.685238144031043</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.766240032543426</v>
+        <v>6.625276698532105</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1043693189633187</v>
+        <v>0.1041867244846522</v>
       </c>
       <c r="C50">
-        <v>60.40272901943185</v>
+        <v>59.67412686307581</v>
       </c>
       <c r="D50">
-        <v>90.72352901943184</v>
+        <v>90.96202686307579</v>
       </c>
       <c r="E50">
-        <v>43.21079999999999</v>
+        <v>44.17789999999999</v>
       </c>
       <c r="F50">
-        <v>46.42079999999999</v>
+        <v>47.38789999999999</v>
       </c>
       <c r="G50">
         <v>16.1</v>
@@ -5643,28 +5643,28 @@
         <v>16.7</v>
       </c>
       <c r="M50">
-        <v>2.52064944</v>
+        <v>2.57316297</v>
       </c>
       <c r="N50">
-        <v>14.17935056</v>
+        <v>14.12683703</v>
       </c>
       <c r="O50">
-        <v>3.1194571232</v>
+        <v>3.1079041466</v>
       </c>
       <c r="P50">
-        <v>11.0598934368</v>
+        <v>11.0189328834</v>
       </c>
       <c r="Q50">
-        <v>13.5598934368</v>
+        <v>13.5189328834</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1616142287756129</v>
+        <v>0.1635946362444161</v>
       </c>
       <c r="T50">
-        <v>1.685238144031043</v>
+        <v>1.71405548575524</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.625276698532105</v>
+        <v>6.490066969990634</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1041867244846522</v>
+        <v>0.1040041300059858</v>
       </c>
       <c r="C51">
-        <v>59.67412686307581</v>
+        <v>58.9467819582382</v>
       </c>
       <c r="D51">
-        <v>90.96202686307579</v>
+        <v>91.2017819582382</v>
       </c>
       <c r="E51">
-        <v>44.17789999999999</v>
+        <v>45.145</v>
       </c>
       <c r="F51">
-        <v>47.38789999999999</v>
+        <v>48.355</v>
       </c>
       <c r="G51">
         <v>16.1</v>
@@ -5725,28 +5725,28 @@
         <v>16.7</v>
       </c>
       <c r="M51">
-        <v>2.57316297</v>
+        <v>2.6256765</v>
       </c>
       <c r="N51">
-        <v>14.12683703</v>
+        <v>14.0743235</v>
       </c>
       <c r="O51">
-        <v>3.1079041466</v>
+        <v>3.09635117</v>
       </c>
       <c r="P51">
-        <v>11.0189328834</v>
+        <v>10.97797233</v>
       </c>
       <c r="Q51">
-        <v>13.5189328834</v>
+        <v>13.47797233</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1635946362444161</v>
+        <v>0.1656542600119715</v>
       </c>
       <c r="T51">
-        <v>1.71405548575524</v>
+        <v>1.744025521148405</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.490066969990634</v>
+        <v>6.360265630590821</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1040041300059858</v>
+        <v>0.1038215355273193</v>
       </c>
       <c r="C52">
-        <v>58.9467819582382</v>
+        <v>58.22070427267403</v>
       </c>
       <c r="D52">
-        <v>91.2017819582382</v>
+        <v>91.44280427267402</v>
       </c>
       <c r="E52">
-        <v>45.145</v>
+        <v>46.1121</v>
       </c>
       <c r="F52">
-        <v>48.355</v>
+        <v>49.3221</v>
       </c>
       <c r="G52">
         <v>16.1</v>
@@ -5807,28 +5807,28 @@
         <v>16.7</v>
       </c>
       <c r="M52">
-        <v>2.6256765</v>
+        <v>2.67819003</v>
       </c>
       <c r="N52">
-        <v>14.0743235</v>
+        <v>14.02180997</v>
       </c>
       <c r="O52">
-        <v>3.09635117</v>
+        <v>3.0847981934</v>
       </c>
       <c r="P52">
-        <v>10.97797233</v>
+        <v>10.9370117766</v>
       </c>
       <c r="Q52">
-        <v>13.47797233</v>
+        <v>13.4370117766</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1656542600119715</v>
+        <v>0.1677979500557536</v>
       </c>
       <c r="T52">
-        <v>1.744025521148405</v>
+        <v>1.775218823292311</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.360265630590821</v>
+        <v>6.235554539794922</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1038215355273193</v>
+        <v>0.1036389410486528</v>
       </c>
       <c r="C53">
-        <v>58.22070427267403</v>
+        <v>57.49590387978605</v>
       </c>
       <c r="D53">
-        <v>91.44280427267402</v>
+        <v>91.68510387978604</v>
       </c>
       <c r="E53">
-        <v>46.1121</v>
+        <v>47.0792</v>
       </c>
       <c r="F53">
-        <v>49.3221</v>
+        <v>50.2892</v>
       </c>
       <c r="G53">
         <v>16.1</v>
@@ -5889,28 +5889,28 @@
         <v>16.7</v>
       </c>
       <c r="M53">
-        <v>2.67819003</v>
+        <v>2.73070356</v>
       </c>
       <c r="N53">
-        <v>14.02180997</v>
+        <v>13.96929644</v>
       </c>
       <c r="O53">
-        <v>3.0847981934</v>
+        <v>3.0732452168</v>
       </c>
       <c r="P53">
-        <v>10.9370117766</v>
+        <v>10.8960512232</v>
       </c>
       <c r="Q53">
-        <v>13.4370117766</v>
+        <v>13.3960512232</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1677979500557536</v>
+        <v>0.1700309605180267</v>
       </c>
       <c r="T53">
-        <v>1.775218823292311</v>
+        <v>1.807711846358881</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.235554539794922</v>
+        <v>6.115640029414251</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1036389410486528</v>
+        <v>0.1038697465699863</v>
       </c>
       <c r="C54">
-        <v>57.49590387978605</v>
+        <v>56.22274264201339</v>
       </c>
       <c r="D54">
-        <v>91.68510387978604</v>
+        <v>91.37904264201337</v>
       </c>
       <c r="E54">
-        <v>47.0792</v>
+        <v>48.0463</v>
       </c>
       <c r="F54">
-        <v>50.2892</v>
+        <v>51.2563</v>
       </c>
       <c r="G54">
         <v>16.1</v>
@@ -5971,45 +5971,45 @@
         <v>16.7</v>
       </c>
       <c r="M54">
-        <v>2.73070356</v>
+        <v>2.83447339</v>
       </c>
       <c r="N54">
-        <v>13.96929644</v>
+        <v>13.86552661</v>
       </c>
       <c r="O54">
-        <v>3.0732452168</v>
+        <v>3.0504158542</v>
       </c>
       <c r="P54">
-        <v>10.8960512232</v>
+        <v>10.8151107558</v>
       </c>
       <c r="Q54">
-        <v>13.3960512232</v>
+        <v>13.3151107558</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1700309605180267</v>
+        <v>0.1723589927020985</v>
       </c>
       <c r="T54">
-        <v>1.807711846358881</v>
+        <v>1.84158755125807</v>
       </c>
       <c r="U54">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>6.115640029414251</v>
+        <v>5.891746967502842</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1038697465699863</v>
+        <v>0.1036949520913198</v>
       </c>
       <c r="C55">
-        <v>56.22274264201339</v>
+        <v>55.48724180796495</v>
       </c>
       <c r="D55">
-        <v>91.37904264201337</v>
+        <v>91.61064180796495</v>
       </c>
       <c r="E55">
-        <v>48.0463</v>
+        <v>49.0134</v>
       </c>
       <c r="F55">
-        <v>51.2563</v>
+        <v>52.2234</v>
       </c>
       <c r="G55">
         <v>16.1</v>
@@ -6053,28 +6053,28 @@
         <v>16.7</v>
       </c>
       <c r="M55">
-        <v>2.83447339</v>
+        <v>2.88795402</v>
       </c>
       <c r="N55">
-        <v>13.86552661</v>
+        <v>13.81204598</v>
       </c>
       <c r="O55">
-        <v>3.0504158542</v>
+        <v>3.0386501156</v>
       </c>
       <c r="P55">
-        <v>10.8151107558</v>
+        <v>10.7733958644</v>
       </c>
       <c r="Q55">
-        <v>13.3151107558</v>
+        <v>13.2733958644</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1723589927020985</v>
+        <v>0.1747882436767823</v>
       </c>
       <c r="T55">
-        <v>1.84158755125807</v>
+        <v>1.876936112892006</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.891746967502842</v>
+        <v>5.782640542178715</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1036949520913198</v>
+        <v>0.1035201576126534</v>
       </c>
       <c r="C56">
-        <v>55.48724180796495</v>
+        <v>54.75291792790723</v>
       </c>
       <c r="D56">
-        <v>91.61064180796495</v>
+        <v>91.84341792790723</v>
       </c>
       <c r="E56">
-        <v>49.0134</v>
+        <v>49.9805</v>
       </c>
       <c r="F56">
-        <v>52.2234</v>
+        <v>53.1905</v>
       </c>
       <c r="G56">
         <v>16.1</v>
@@ -6135,28 +6135,28 @@
         <v>16.7</v>
       </c>
       <c r="M56">
-        <v>2.88795402</v>
+        <v>2.94143465</v>
       </c>
       <c r="N56">
-        <v>13.81204598</v>
+        <v>13.75856535</v>
       </c>
       <c r="O56">
-        <v>3.0386501156</v>
+        <v>3.026884377</v>
       </c>
       <c r="P56">
-        <v>10.7733958644</v>
+        <v>10.731680973</v>
       </c>
       <c r="Q56">
-        <v>13.2733958644</v>
+        <v>13.231680973</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1747882436767823</v>
+        <v>0.1773254613614519</v>
       </c>
       <c r="T56">
-        <v>1.876936112892006</v>
+        <v>1.913855721709673</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.782640542178715</v>
+        <v>5.677501623230011</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1035201576126534</v>
+        <v>0.1033453631339869</v>
       </c>
       <c r="C57">
-        <v>54.75291792790723</v>
+        <v>54.01977999636358</v>
       </c>
       <c r="D57">
-        <v>91.84341792790723</v>
+        <v>92.07737999636359</v>
       </c>
       <c r="E57">
-        <v>49.9805</v>
+        <v>50.9476</v>
       </c>
       <c r="F57">
-        <v>53.1905</v>
+        <v>54.1576</v>
       </c>
       <c r="G57">
         <v>16.1</v>
@@ -6217,28 +6217,28 @@
         <v>16.7</v>
       </c>
       <c r="M57">
-        <v>2.94143465</v>
+        <v>2.99491528</v>
       </c>
       <c r="N57">
-        <v>13.75856535</v>
+        <v>13.70508472</v>
       </c>
       <c r="O57">
-        <v>3.026884377</v>
+        <v>3.0151186384</v>
       </c>
       <c r="P57">
-        <v>10.731680973</v>
+        <v>10.6899660816</v>
       </c>
       <c r="Q57">
-        <v>13.231680973</v>
+        <v>13.1899660816</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1773254613614519</v>
+        <v>0.1799780071226974</v>
       </c>
       <c r="T57">
-        <v>1.913855721709673</v>
+        <v>1.952453494564507</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.677501623230011</v>
+        <v>5.576117665672331</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1033453631339869</v>
+        <v>0.1031705686553204</v>
       </c>
       <c r="C58">
-        <v>54.01977999636358</v>
+        <v>53.28783709974208</v>
       </c>
       <c r="D58">
-        <v>92.07737999636359</v>
+        <v>92.31253709974209</v>
       </c>
       <c r="E58">
-        <v>50.9476</v>
+        <v>51.9147</v>
       </c>
       <c r="F58">
-        <v>54.1576</v>
+        <v>55.1247</v>
       </c>
       <c r="G58">
         <v>16.1</v>
@@ -6299,28 +6299,28 @@
         <v>16.7</v>
       </c>
       <c r="M58">
-        <v>2.99491528</v>
+        <v>3.04839591</v>
       </c>
       <c r="N58">
-        <v>13.70508472</v>
+        <v>13.65160409</v>
       </c>
       <c r="O58">
-        <v>3.0151186384</v>
+        <v>3.0033528998</v>
       </c>
       <c r="P58">
-        <v>10.6899660816</v>
+        <v>10.6482511902</v>
       </c>
       <c r="Q58">
-        <v>13.1899660816</v>
+        <v>13.1482511902</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1799780071226974</v>
+        <v>0.1827539271053963</v>
       </c>
       <c r="T58">
-        <v>1.952453494564507</v>
+        <v>1.992846512668403</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.576117665672331</v>
+        <v>5.478291039958782</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1031705686553204</v>
+        <v>0.1029957741766539</v>
       </c>
       <c r="C59">
-        <v>53.28783709974208</v>
+        <v>52.5570984175119</v>
       </c>
       <c r="D59">
-        <v>92.31253709974209</v>
+        <v>92.54889841751189</v>
       </c>
       <c r="E59">
-        <v>51.9147</v>
+        <v>52.88180000000001</v>
       </c>
       <c r="F59">
-        <v>55.1247</v>
+        <v>56.09180000000001</v>
       </c>
       <c r="G59">
         <v>16.1</v>
@@ -6381,28 +6381,28 @@
         <v>16.7</v>
       </c>
       <c r="M59">
-        <v>3.04839591</v>
+        <v>3.101876540000001</v>
       </c>
       <c r="N59">
-        <v>13.65160409</v>
+        <v>13.59812346</v>
       </c>
       <c r="O59">
-        <v>3.0033528998</v>
+        <v>2.9915871612</v>
       </c>
       <c r="P59">
-        <v>10.6482511902</v>
+        <v>10.6065362988</v>
       </c>
       <c r="Q59">
-        <v>13.1482511902</v>
+        <v>13.1065362988</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1827539271053963</v>
+        <v>0.1856620337539379</v>
       </c>
       <c r="T59">
-        <v>1.992846512668403</v>
+        <v>2.035163007824865</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.478291039958782</v>
+        <v>5.383837746166389</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1029957741766539</v>
+        <v>0.1028209796979874</v>
       </c>
       <c r="C60">
-        <v>52.55709841751191</v>
+        <v>51.82757322339768</v>
       </c>
       <c r="D60">
-        <v>92.54889841751191</v>
+        <v>92.78647322339768</v>
       </c>
       <c r="E60">
-        <v>52.88179999999999</v>
+        <v>53.84889999999999</v>
       </c>
       <c r="F60">
-        <v>56.09179999999999</v>
+        <v>57.05889999999999</v>
       </c>
       <c r="G60">
         <v>16.1</v>
@@ -6463,28 +6463,28 @@
         <v>16.7</v>
       </c>
       <c r="M60">
-        <v>3.10187654</v>
+        <v>3.15535717</v>
       </c>
       <c r="N60">
-        <v>13.59812346</v>
+        <v>13.54464283</v>
       </c>
       <c r="O60">
-        <v>2.9915871612</v>
+        <v>2.9798214226</v>
       </c>
       <c r="P60">
-        <v>10.6065362988</v>
+        <v>10.5648214074</v>
       </c>
       <c r="Q60">
-        <v>13.1065362988</v>
+        <v>13.0648214074</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1856620337539379</v>
+        <v>0.1887119992633839</v>
       </c>
       <c r="T60">
-        <v>2.035163007824864</v>
+        <v>2.079543722257251</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.383837746166391</v>
+        <v>5.29258625894323</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1028209796979874</v>
+        <v>0.1026461852193209</v>
       </c>
       <c r="C61">
-        <v>51.82757322339768</v>
+        <v>51.09927088659252</v>
       </c>
       <c r="D61">
-        <v>92.78647322339768</v>
+        <v>93.02527088659252</v>
       </c>
       <c r="E61">
-        <v>53.84889999999999</v>
+        <v>54.816</v>
       </c>
       <c r="F61">
-        <v>57.05889999999999</v>
+        <v>58.026</v>
       </c>
       <c r="G61">
         <v>16.1</v>
@@ -6545,28 +6545,28 @@
         <v>16.7</v>
       </c>
       <c r="M61">
-        <v>3.15535717</v>
+        <v>3.2088378</v>
       </c>
       <c r="N61">
-        <v>13.54464283</v>
+        <v>13.4911622</v>
       </c>
       <c r="O61">
-        <v>2.9798214226</v>
+        <v>2.968055684</v>
       </c>
       <c r="P61">
-        <v>10.5648214074</v>
+        <v>10.523106516</v>
       </c>
       <c r="Q61">
-        <v>13.0648214074</v>
+        <v>13.023106516</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1887119992633839</v>
+        <v>0.1919144630483023</v>
       </c>
       <c r="T61">
-        <v>2.079543722257251</v>
+        <v>2.126143472411258</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.29258625894323</v>
+        <v>5.204376487960843</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1026461852193209</v>
+        <v>0.1024713907406545</v>
       </c>
       <c r="C62">
-        <v>51.09927088659252</v>
+        <v>50.37220087298942</v>
       </c>
       <c r="D62">
-        <v>93.02527088659252</v>
+        <v>93.26530087298941</v>
       </c>
       <c r="E62">
-        <v>54.816</v>
+        <v>55.7831</v>
       </c>
       <c r="F62">
-        <v>58.026</v>
+        <v>58.9931</v>
       </c>
       <c r="G62">
         <v>16.1</v>
@@ -6627,28 +6627,28 @@
         <v>16.7</v>
       </c>
       <c r="M62">
-        <v>3.2088378</v>
+        <v>3.26231843</v>
       </c>
       <c r="N62">
-        <v>13.4911622</v>
+        <v>13.43768157</v>
       </c>
       <c r="O62">
-        <v>2.968055684</v>
+        <v>2.9562899454</v>
       </c>
       <c r="P62">
-        <v>10.523106516</v>
+        <v>10.4813916246</v>
       </c>
       <c r="Q62">
-        <v>13.023106516</v>
+        <v>12.9813916246</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1919144630483023</v>
+        <v>0.1952811557452678</v>
       </c>
       <c r="T62">
-        <v>2.126143472411258</v>
+        <v>2.175132953342393</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.204376487960843</v>
+        <v>5.119058840617223</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1024713907406545</v>
+        <v>0.102296596261988</v>
       </c>
       <c r="C63">
-        <v>50.37220087298942</v>
+        <v>49.64637274643245</v>
       </c>
       <c r="D63">
-        <v>93.26530087298941</v>
+        <v>93.50657274643244</v>
       </c>
       <c r="E63">
-        <v>55.7831</v>
+        <v>56.75019999999999</v>
       </c>
       <c r="F63">
-        <v>58.9931</v>
+        <v>59.96019999999999</v>
       </c>
       <c r="G63">
         <v>16.1</v>
@@ -6709,28 +6709,28 @@
         <v>16.7</v>
       </c>
       <c r="M63">
-        <v>3.26231843</v>
+        <v>3.31579906</v>
       </c>
       <c r="N63">
-        <v>13.43768157</v>
+        <v>13.38420094</v>
       </c>
       <c r="O63">
-        <v>2.9562899454</v>
+        <v>2.9445242068</v>
       </c>
       <c r="P63">
-        <v>10.4813916246</v>
+        <v>10.4396767332</v>
       </c>
       <c r="Q63">
-        <v>12.9813916246</v>
+        <v>12.9396767332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1952811557452678</v>
+        <v>0.1988250427947052</v>
       </c>
       <c r="T63">
-        <v>2.175132953342393</v>
+        <v>2.226700828006745</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.119058840617223</v>
+        <v>5.036493375445978</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.102296596261988</v>
+        <v>0.1021218017833215</v>
       </c>
       <c r="C64">
-        <v>49.64637274643245</v>
+        <v>48.9217961699865</v>
       </c>
       <c r="D64">
-        <v>93.50657274643244</v>
+        <v>93.74909616998649</v>
       </c>
       <c r="E64">
-        <v>56.75019999999999</v>
+        <v>57.71729999999999</v>
       </c>
       <c r="F64">
-        <v>59.96019999999999</v>
+        <v>60.9273</v>
       </c>
       <c r="G64">
         <v>16.1</v>
@@ -6791,28 +6791,28 @@
         <v>16.7</v>
       </c>
       <c r="M64">
-        <v>3.31579906</v>
+        <v>3.36927969</v>
       </c>
       <c r="N64">
-        <v>13.38420094</v>
+        <v>13.33072031</v>
       </c>
       <c r="O64">
-        <v>2.9445242068</v>
+        <v>2.9327584682</v>
       </c>
       <c r="P64">
-        <v>10.4396767332</v>
+        <v>10.3979618418</v>
       </c>
       <c r="Q64">
-        <v>12.9396767332</v>
+        <v>12.8979618418</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1988250427947052</v>
+        <v>0.2025604913062743</v>
       </c>
       <c r="T64">
-        <v>2.226700828006745</v>
+        <v>2.281056155355658</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.036493375445978</v>
+        <v>4.956549036153184</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1021218017833215</v>
+        <v>0.101947007304655</v>
       </c>
       <c r="C65">
-        <v>48.9217961699865</v>
+        <v>48.19848090722791</v>
       </c>
       <c r="D65">
-        <v>93.74909616998649</v>
+        <v>93.9928809072279</v>
       </c>
       <c r="E65">
-        <v>57.71729999999999</v>
+        <v>58.6844</v>
       </c>
       <c r="F65">
-        <v>60.9273</v>
+        <v>61.8944</v>
       </c>
       <c r="G65">
         <v>16.1</v>
@@ -6873,28 +6873,28 @@
         <v>16.7</v>
       </c>
       <c r="M65">
-        <v>3.36927969</v>
+        <v>3.42276032</v>
       </c>
       <c r="N65">
-        <v>13.33072031</v>
+        <v>13.27723968</v>
       </c>
       <c r="O65">
-        <v>2.9327584682</v>
+        <v>2.9209927296</v>
       </c>
       <c r="P65">
-        <v>10.3979618418</v>
+        <v>10.3562469504</v>
       </c>
       <c r="Q65">
-        <v>12.8979618418</v>
+        <v>12.8562469504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2025604913062743</v>
+        <v>0.2065034647351528</v>
       </c>
       <c r="T65">
-        <v>2.281056155355658</v>
+        <v>2.338431223112843</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.956549036153184</v>
+        <v>4.87910295746329</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.101947007304655</v>
+        <v>0.1017722128259885</v>
       </c>
       <c r="C66">
-        <v>48.19848090722791</v>
+        <v>47.4764368235542</v>
       </c>
       <c r="D66">
-        <v>93.9928809072279</v>
+        <v>94.23793682355421</v>
       </c>
       <c r="E66">
-        <v>58.6844</v>
+        <v>59.6515</v>
       </c>
       <c r="F66">
-        <v>61.8944</v>
+        <v>62.8615</v>
       </c>
       <c r="G66">
         <v>16.1</v>
@@ -6955,28 +6955,28 @@
         <v>16.7</v>
       </c>
       <c r="M66">
-        <v>3.42276032</v>
+        <v>3.47624095</v>
       </c>
       <c r="N66">
-        <v>13.27723968</v>
+        <v>13.22375905</v>
       </c>
       <c r="O66">
-        <v>2.9209927296</v>
+        <v>2.909226991</v>
       </c>
       <c r="P66">
-        <v>10.3562469504</v>
+        <v>10.314532059</v>
       </c>
       <c r="Q66">
-        <v>12.8562469504</v>
+        <v>12.814532059</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2065034647351528</v>
+        <v>0.2106717509313958</v>
       </c>
       <c r="T66">
-        <v>2.338431223112843</v>
+        <v>2.399084866170439</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.87910295746329</v>
+        <v>4.804039835040777</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1017722128259885</v>
+        <v>0.1015974183473221</v>
       </c>
       <c r="C67">
-        <v>47.4764368235542</v>
+        <v>46.75567388751534</v>
       </c>
       <c r="D67">
-        <v>94.23793682355421</v>
+        <v>94.48427388751533</v>
       </c>
       <c r="E67">
-        <v>59.6515</v>
+        <v>60.6186</v>
       </c>
       <c r="F67">
-        <v>62.8615</v>
+        <v>63.8286</v>
       </c>
       <c r="G67">
         <v>16.1</v>
@@ -7037,28 +7037,28 @@
         <v>16.7</v>
       </c>
       <c r="M67">
-        <v>3.47624095</v>
+        <v>3.52972158</v>
       </c>
       <c r="N67">
-        <v>13.22375905</v>
+        <v>13.17027842</v>
       </c>
       <c r="O67">
-        <v>2.909226991</v>
+        <v>2.8974612524</v>
       </c>
       <c r="P67">
-        <v>10.314532059</v>
+        <v>10.2728171676</v>
       </c>
       <c r="Q67">
-        <v>12.814532059</v>
+        <v>12.7728171676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2106717509313958</v>
+        <v>0.2150852304333002</v>
       </c>
       <c r="T67">
-        <v>2.399084866170439</v>
+        <v>2.463306370584363</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.804039835040777</v>
+        <v>4.731251352691675</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1015974183473221</v>
+        <v>0.1014226238686556</v>
       </c>
       <c r="C68">
-        <v>46.75567388751534</v>
+        <v>46.03620217216501</v>
       </c>
       <c r="D68">
-        <v>94.48427388751533</v>
+        <v>94.73190217216499</v>
       </c>
       <c r="E68">
-        <v>60.6186</v>
+        <v>61.5857</v>
       </c>
       <c r="F68">
-        <v>63.8286</v>
+        <v>64.7957</v>
       </c>
       <c r="G68">
         <v>16.1</v>
@@ -7119,28 +7119,28 @@
         <v>16.7</v>
       </c>
       <c r="M68">
-        <v>3.52972158</v>
+        <v>3.58320221</v>
       </c>
       <c r="N68">
-        <v>13.17027842</v>
+        <v>13.11679779</v>
       </c>
       <c r="O68">
-        <v>2.8974612524</v>
+        <v>2.8856955138</v>
       </c>
       <c r="P68">
-        <v>10.2728171676</v>
+        <v>10.2311022762</v>
       </c>
       <c r="Q68">
-        <v>12.7728171676</v>
+        <v>12.7311022762</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2150852304333002</v>
+        <v>0.2197661935413805</v>
       </c>
       <c r="T68">
-        <v>2.463306370584363</v>
+        <v>2.531420087387011</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.731251352691675</v>
+        <v>4.660635660860457</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1014226238686556</v>
+        <v>0.1012478293899891</v>
       </c>
       <c r="C69">
-        <v>46.03620217216501</v>
+        <v>45.31803185643406</v>
       </c>
       <c r="D69">
-        <v>94.73190217216499</v>
+        <v>94.98083185643407</v>
       </c>
       <c r="E69">
-        <v>61.5857</v>
+        <v>62.5528</v>
       </c>
       <c r="F69">
-        <v>64.7957</v>
+        <v>65.7628</v>
       </c>
       <c r="G69">
         <v>16.1</v>
@@ -7201,28 +7201,28 @@
         <v>16.7</v>
       </c>
       <c r="M69">
-        <v>3.58320221</v>
+        <v>3.63668284</v>
       </c>
       <c r="N69">
-        <v>13.11679779</v>
+        <v>13.06331716</v>
       </c>
       <c r="O69">
-        <v>2.8856955138</v>
+        <v>2.8739297752</v>
       </c>
       <c r="P69">
-        <v>10.2311022762</v>
+        <v>10.1893873848</v>
       </c>
       <c r="Q69">
-        <v>12.7311022762</v>
+        <v>12.6893873848</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2197661935413805</v>
+        <v>0.2247397168437159</v>
       </c>
       <c r="T69">
-        <v>2.531420087387011</v>
+        <v>2.603790911489825</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.660635660860457</v>
+        <v>4.59209690114192</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1012478293899891</v>
+        <v>0.1010730349113226</v>
       </c>
       <c r="C70">
-        <v>45.31803185643406</v>
+        <v>44.60117322652498</v>
       </c>
       <c r="D70">
-        <v>94.98083185643407</v>
+        <v>95.23107322652497</v>
       </c>
       <c r="E70">
-        <v>62.5528</v>
+        <v>63.5199</v>
       </c>
       <c r="F70">
-        <v>65.7628</v>
+        <v>66.7299</v>
       </c>
       <c r="G70">
         <v>16.1</v>
@@ -7283,28 +7283,28 @@
         <v>16.7</v>
       </c>
       <c r="M70">
-        <v>3.63668284</v>
+        <v>3.69016347</v>
       </c>
       <c r="N70">
-        <v>13.06331716</v>
+        <v>13.00983653</v>
       </c>
       <c r="O70">
-        <v>2.8739297752</v>
+        <v>2.8621640366</v>
       </c>
       <c r="P70">
-        <v>10.1893873848</v>
+        <v>10.1476724934</v>
       </c>
       <c r="Q70">
-        <v>12.6893873848</v>
+        <v>12.6476724934</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2247397168437159</v>
+        <v>0.2300341126171697</v>
       </c>
       <c r="T70">
-        <v>2.603790911489825</v>
+        <v>2.680830821018625</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.59209690114192</v>
+        <v>4.525544772139863</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1010730349113226</v>
+        <v>0.1022632404326561</v>
       </c>
       <c r="C71">
-        <v>44.60117322652498</v>
+        <v>41.95575628667353</v>
       </c>
       <c r="D71">
-        <v>95.23107322652497</v>
+        <v>93.55275628667353</v>
       </c>
       <c r="E71">
-        <v>63.5199</v>
+        <v>64.48700000000001</v>
       </c>
       <c r="F71">
-        <v>66.7299</v>
+        <v>67.697</v>
       </c>
       <c r="G71">
         <v>16.1</v>
@@ -7365,45 +7365,45 @@
         <v>16.7</v>
       </c>
       <c r="M71">
-        <v>3.69016347</v>
+        <v>3.912886600000001</v>
       </c>
       <c r="N71">
-        <v>13.00983653</v>
+        <v>12.7871134</v>
       </c>
       <c r="O71">
-        <v>2.8621640366</v>
+        <v>2.813164948</v>
       </c>
       <c r="P71">
-        <v>10.1476724934</v>
+        <v>9.973948451999998</v>
       </c>
       <c r="Q71">
-        <v>12.6476724934</v>
+        <v>12.473948452</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2300341126171697</v>
+        <v>0.2356814681088538</v>
       </c>
       <c r="T71">
-        <v>2.680830821018625</v>
+        <v>2.763006724516013</v>
       </c>
       <c r="U71">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.525544772139863</v>
+        <v>4.267948884590726</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1022632404326561</v>
+        <v>0.1021079459539896</v>
       </c>
       <c r="C72">
-        <v>41.95575628667353</v>
+        <v>41.20427464843324</v>
       </c>
       <c r="D72">
-        <v>93.55275628667353</v>
+        <v>93.76837464843324</v>
       </c>
       <c r="E72">
-        <v>64.48700000000001</v>
+        <v>65.45410000000001</v>
       </c>
       <c r="F72">
-        <v>67.697</v>
+        <v>68.6641</v>
       </c>
       <c r="G72">
         <v>16.1</v>
@@ -7447,28 +7447,28 @@
         <v>16.7</v>
       </c>
       <c r="M72">
-        <v>3.912886600000001</v>
+        <v>3.968784980000001</v>
       </c>
       <c r="N72">
-        <v>12.7871134</v>
+        <v>12.73121502</v>
       </c>
       <c r="O72">
-        <v>2.813164948</v>
+        <v>2.8008673044</v>
       </c>
       <c r="P72">
-        <v>9.973948451999998</v>
+        <v>9.9303477156</v>
       </c>
       <c r="Q72">
-        <v>12.473948452</v>
+        <v>12.4303477156</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2356814681088538</v>
+        <v>0.2417182963930678</v>
       </c>
       <c r="T72">
-        <v>2.763006724516013</v>
+        <v>2.850849931702876</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.267948884590726</v>
+        <v>4.20783692846973</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1021079459539897</v>
+        <v>0.1019526514753232</v>
       </c>
       <c r="C73">
-        <v>41.20427464843323</v>
+        <v>40.45378921125423</v>
       </c>
       <c r="D73">
-        <v>93.76837464843322</v>
+        <v>93.98498921125422</v>
       </c>
       <c r="E73">
-        <v>65.4541</v>
+        <v>66.4212</v>
       </c>
       <c r="F73">
-        <v>68.66409999999999</v>
+        <v>69.63119999999999</v>
       </c>
       <c r="G73">
         <v>16.1</v>
@@ -7529,28 +7529,28 @@
         <v>16.7</v>
       </c>
       <c r="M73">
-        <v>3.96878498</v>
+        <v>4.02468336</v>
       </c>
       <c r="N73">
-        <v>12.73121502</v>
+        <v>12.67531664</v>
       </c>
       <c r="O73">
-        <v>2.8008673044</v>
+        <v>2.788569660799999</v>
       </c>
       <c r="P73">
-        <v>9.9303477156</v>
+        <v>9.886746979199998</v>
       </c>
       <c r="Q73">
-        <v>12.4303477156</v>
+        <v>12.3867469792</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2417182963930677</v>
+        <v>0.2481863266975827</v>
       </c>
       <c r="T73">
-        <v>2.850849931702875</v>
+        <v>2.9449676536888</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.207836928469731</v>
+        <v>4.14939474890765</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1019526514753232</v>
+        <v>0.1017973569966567</v>
       </c>
       <c r="C74">
-        <v>40.45378921125423</v>
+        <v>39.70430689510221</v>
       </c>
       <c r="D74">
-        <v>93.98498921125422</v>
+        <v>94.20260689510219</v>
       </c>
       <c r="E74">
-        <v>66.4212</v>
+        <v>67.3883</v>
       </c>
       <c r="F74">
-        <v>69.63119999999999</v>
+        <v>70.59829999999999</v>
       </c>
       <c r="G74">
         <v>16.1</v>
@@ -7611,28 +7611,28 @@
         <v>16.7</v>
       </c>
       <c r="M74">
-        <v>4.02468336</v>
+        <v>4.08058174</v>
       </c>
       <c r="N74">
-        <v>12.67531664</v>
+        <v>12.61941826</v>
       </c>
       <c r="O74">
-        <v>2.788569660799999</v>
+        <v>2.7762720172</v>
       </c>
       <c r="P74">
-        <v>9.886746979199998</v>
+        <v>9.8431462428</v>
       </c>
       <c r="Q74">
-        <v>12.3867469792</v>
+        <v>12.3431462428</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2481863266975827</v>
+        <v>0.2551334703579877</v>
       </c>
       <c r="T74">
-        <v>2.9449676536888</v>
+        <v>3.046057058784792</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.14939474890765</v>
+        <v>4.092553724950012</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1017973569966567</v>
+        <v>0.1016420625179902</v>
       </c>
       <c r="C75">
-        <v>39.70430689510221</v>
+        <v>38.95583468418299</v>
       </c>
       <c r="D75">
-        <v>94.20260689510219</v>
+        <v>94.42123468418299</v>
       </c>
       <c r="E75">
-        <v>67.3883</v>
+        <v>68.3554</v>
       </c>
       <c r="F75">
-        <v>70.59829999999999</v>
+        <v>71.5654</v>
       </c>
       <c r="G75">
         <v>16.1</v>
@@ -7693,28 +7693,28 @@
         <v>16.7</v>
       </c>
       <c r="M75">
-        <v>4.08058174</v>
+        <v>4.13648012</v>
       </c>
       <c r="N75">
-        <v>12.61941826</v>
+        <v>12.56351988</v>
       </c>
       <c r="O75">
-        <v>2.7762720172</v>
+        <v>2.7639743736</v>
       </c>
       <c r="P75">
-        <v>9.8431462428</v>
+        <v>9.799545506399999</v>
       </c>
       <c r="Q75">
-        <v>12.3431462428</v>
+        <v>12.2995455064</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2551334703579877</v>
+        <v>0.2626150096845776</v>
       </c>
       <c r="T75">
-        <v>3.046057058784792</v>
+        <v>3.154922571965092</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.092553724950012</v>
+        <v>4.037248944883119</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1016420625179902</v>
+        <v>0.1035342680393237</v>
       </c>
       <c r="C76">
-        <v>38.95583468418299</v>
+        <v>35.3920830027082</v>
       </c>
       <c r="D76">
-        <v>94.42123468418299</v>
+        <v>91.8245830027082</v>
       </c>
       <c r="E76">
-        <v>68.3554</v>
+        <v>69.32250000000001</v>
       </c>
       <c r="F76">
-        <v>71.5654</v>
+        <v>72.5325</v>
       </c>
       <c r="G76">
         <v>16.1</v>
@@ -7775,45 +7775,45 @@
         <v>16.7</v>
       </c>
       <c r="M76">
-        <v>4.13648012</v>
+        <v>4.44624225</v>
       </c>
       <c r="N76">
-        <v>12.56351988</v>
+        <v>12.25375775</v>
       </c>
       <c r="O76">
-        <v>2.7639743736</v>
+        <v>2.695826705</v>
       </c>
       <c r="P76">
-        <v>9.799545506399999</v>
+        <v>9.557931044999998</v>
       </c>
       <c r="Q76">
-        <v>12.2995455064</v>
+        <v>12.057931045</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2626150096845776</v>
+        <v>0.2706950721572948</v>
       </c>
       <c r="T76">
-        <v>3.154922571965092</v>
+        <v>3.272497326199816</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.22</v>
       </c>
       <c r="W76">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.037248944883119</v>
+        <v>3.755980682339114</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1035342680393237</v>
+        <v>0.1034062735606572</v>
       </c>
       <c r="C77">
-        <v>35.3920830027082</v>
+        <v>34.5961163154149</v>
       </c>
       <c r="D77">
-        <v>91.8245830027082</v>
+        <v>91.9957163154149</v>
       </c>
       <c r="E77">
-        <v>69.32250000000001</v>
+        <v>70.28960000000001</v>
       </c>
       <c r="F77">
-        <v>72.5325</v>
+        <v>73.4996</v>
       </c>
       <c r="G77">
         <v>16.1</v>
@@ -7857,28 +7857,28 @@
         <v>16.7</v>
       </c>
       <c r="M77">
-        <v>4.44624225</v>
+        <v>4.50552548</v>
       </c>
       <c r="N77">
-        <v>12.25375775</v>
+        <v>12.19447452</v>
       </c>
       <c r="O77">
-        <v>2.695826705</v>
+        <v>2.6827843944</v>
       </c>
       <c r="P77">
-        <v>9.557931044999998</v>
+        <v>9.511690125599999</v>
       </c>
       <c r="Q77">
-        <v>12.057931045</v>
+        <v>12.0116901256</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2706950721572948</v>
+        <v>0.2794484731694051</v>
       </c>
       <c r="T77">
-        <v>3.272497326199816</v>
+        <v>3.399869976620767</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.755980682339114</v>
+        <v>3.706559883887284</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1034062735606572</v>
+        <v>0.1032782790819907</v>
       </c>
       <c r="C78">
-        <v>34.5961163154149</v>
+        <v>33.80078870086393</v>
       </c>
       <c r="D78">
-        <v>91.9957163154149</v>
+        <v>92.16748870086393</v>
       </c>
       <c r="E78">
-        <v>70.28960000000001</v>
+        <v>71.25670000000001</v>
       </c>
       <c r="F78">
-        <v>73.4996</v>
+        <v>74.4667</v>
       </c>
       <c r="G78">
         <v>16.1</v>
@@ -7939,28 +7939,28 @@
         <v>16.7</v>
       </c>
       <c r="M78">
-        <v>4.50552548</v>
+        <v>4.56480871</v>
       </c>
       <c r="N78">
-        <v>12.19447452</v>
+        <v>12.13519129</v>
       </c>
       <c r="O78">
-        <v>2.6827843944</v>
+        <v>2.6697420838</v>
       </c>
       <c r="P78">
-        <v>9.511690125599999</v>
+        <v>9.465449206199999</v>
       </c>
       <c r="Q78">
-        <v>12.0116901256</v>
+        <v>11.9654492062</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2794484731694051</v>
+        <v>0.2889630394869163</v>
       </c>
       <c r="T78">
-        <v>3.399869976620767</v>
+        <v>3.538318509687018</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.706559883887284</v>
+        <v>3.658422742538098</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1032782790819907</v>
+        <v>0.1031502846033243</v>
       </c>
       <c r="C79">
-        <v>33.80078870086393</v>
+        <v>33.00610374553972</v>
       </c>
       <c r="D79">
-        <v>92.16748870086393</v>
+        <v>92.33990374553971</v>
       </c>
       <c r="E79">
-        <v>71.25670000000001</v>
+        <v>72.2238</v>
       </c>
       <c r="F79">
-        <v>74.4667</v>
+        <v>75.43379999999999</v>
       </c>
       <c r="G79">
         <v>16.1</v>
@@ -8021,28 +8021,28 @@
         <v>16.7</v>
       </c>
       <c r="M79">
-        <v>4.56480871</v>
+        <v>4.62409194</v>
       </c>
       <c r="N79">
-        <v>12.13519129</v>
+        <v>12.07590806</v>
       </c>
       <c r="O79">
-        <v>2.6697420838</v>
+        <v>2.6566997732</v>
       </c>
       <c r="P79">
-        <v>9.465449206199999</v>
+        <v>9.4192082868</v>
       </c>
       <c r="Q79">
-        <v>11.9654492062</v>
+        <v>11.9192082868</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2889630394869163</v>
+        <v>0.2993425663787467</v>
       </c>
       <c r="T79">
-        <v>3.538318509687018</v>
+        <v>3.68935327303202</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.658422742538098</v>
+        <v>3.611519886864533</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1031502846033243</v>
+        <v>0.1030222901246578</v>
       </c>
       <c r="C80">
-        <v>33.00610374553972</v>
+        <v>32.21206506281361</v>
       </c>
       <c r="D80">
-        <v>92.33990374553971</v>
+        <v>92.51296506281361</v>
       </c>
       <c r="E80">
-        <v>72.2238</v>
+        <v>73.1909</v>
       </c>
       <c r="F80">
-        <v>75.43379999999999</v>
+        <v>76.40089999999999</v>
       </c>
       <c r="G80">
         <v>16.1</v>
@@ -8103,28 +8103,28 @@
         <v>16.7</v>
       </c>
       <c r="M80">
-        <v>4.62409194</v>
+        <v>4.68337517</v>
       </c>
       <c r="N80">
-        <v>12.07590806</v>
+        <v>12.01662483</v>
       </c>
       <c r="O80">
-        <v>2.6566997732</v>
+        <v>2.6436574626</v>
       </c>
       <c r="P80">
-        <v>9.4192082868</v>
+        <v>9.372967367399999</v>
       </c>
       <c r="Q80">
-        <v>11.9192082868</v>
+        <v>11.8729673674</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2993425663787467</v>
+        <v>0.3107106196412276</v>
       </c>
       <c r="T80">
-        <v>3.68935327303202</v>
+        <v>3.854772299552735</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.611519886864533</v>
+        <v>3.565804445258653</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1030222901246578</v>
+        <v>0.1028942956459913</v>
       </c>
       <c r="C81">
-        <v>32.21206506281361</v>
+        <v>31.41867629319611</v>
       </c>
       <c r="D81">
-        <v>92.51296506281361</v>
+        <v>92.6866762931961</v>
       </c>
       <c r="E81">
-        <v>73.1909</v>
+        <v>74.158</v>
       </c>
       <c r="F81">
-        <v>76.40089999999999</v>
+        <v>77.36799999999999</v>
       </c>
       <c r="G81">
         <v>16.1</v>
@@ -8185,28 +8185,28 @@
         <v>16.7</v>
       </c>
       <c r="M81">
-        <v>4.68337517</v>
+        <v>4.7426584</v>
       </c>
       <c r="N81">
-        <v>12.01662483</v>
+        <v>11.9573416</v>
       </c>
       <c r="O81">
-        <v>2.6436574626</v>
+        <v>2.630615152</v>
       </c>
       <c r="P81">
-        <v>9.372967367399999</v>
+        <v>9.326726447999999</v>
       </c>
       <c r="Q81">
-        <v>11.8729673674</v>
+        <v>11.826726448</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3107106196412276</v>
+        <v>0.3232154782299566</v>
       </c>
       <c r="T81">
-        <v>3.854772299552735</v>
+        <v>4.036733228725523</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.565804445258653</v>
+        <v>3.52123188969292</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1028942956459913</v>
+        <v>0.1045353411673248</v>
       </c>
       <c r="C82">
-        <v>31.41867629319611</v>
+        <v>28.27266020305088</v>
       </c>
       <c r="D82">
-        <v>92.6866762931961</v>
+        <v>90.50776020305086</v>
       </c>
       <c r="E82">
-        <v>74.158</v>
+        <v>75.1251</v>
       </c>
       <c r="F82">
-        <v>77.36799999999999</v>
+        <v>78.3351</v>
       </c>
       <c r="G82">
         <v>16.1</v>
@@ -8267,45 +8267,45 @@
         <v>16.7</v>
       </c>
       <c r="M82">
-        <v>4.7426584</v>
+        <v>5.021279910000001</v>
       </c>
       <c r="N82">
-        <v>11.9573416</v>
+        <v>11.67872009</v>
       </c>
       <c r="O82">
-        <v>2.630615152</v>
+        <v>2.5693184198</v>
       </c>
       <c r="P82">
-        <v>9.326726447999999</v>
+        <v>9.109401670199999</v>
       </c>
       <c r="Q82">
-        <v>11.826726448</v>
+        <v>11.6094016702</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3232154782299566</v>
+        <v>0.3370366377227623</v>
       </c>
       <c r="T82">
-        <v>4.036733228725523</v>
+        <v>4.237847939916498</v>
       </c>
       <c r="U82">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.52123188969292</v>
+        <v>3.325845262428319</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1045353411673248</v>
+        <v>0.1044291866886583</v>
       </c>
       <c r="C83">
-        <v>28.27266020305088</v>
+        <v>27.4434041304861</v>
       </c>
       <c r="D83">
-        <v>90.50776020305086</v>
+        <v>90.64560413048611</v>
       </c>
       <c r="E83">
-        <v>75.1251</v>
+        <v>76.09220000000001</v>
       </c>
       <c r="F83">
-        <v>78.3351</v>
+        <v>79.3022</v>
       </c>
       <c r="G83">
         <v>16.1</v>
@@ -8349,28 +8349,28 @@
         <v>16.7</v>
       </c>
       <c r="M83">
-        <v>5.021279910000001</v>
+        <v>5.083271020000001</v>
       </c>
       <c r="N83">
-        <v>11.67872009</v>
+        <v>11.61672898</v>
       </c>
       <c r="O83">
-        <v>2.5693184198</v>
+        <v>2.5556803756</v>
       </c>
       <c r="P83">
-        <v>9.109401670199999</v>
+        <v>9.061048604399998</v>
       </c>
       <c r="Q83">
-        <v>11.6094016702</v>
+        <v>11.5610486044</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3370366377227623</v>
+        <v>0.3523934816036575</v>
       </c>
       <c r="T83">
-        <v>4.237847939916498</v>
+        <v>4.461308730128692</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.325845262428319</v>
+        <v>3.28528617386212</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1044291866886583</v>
+        <v>0.1043230322099919</v>
       </c>
       <c r="C84">
-        <v>27.4434041304861</v>
+        <v>26.61456857282523</v>
       </c>
       <c r="D84">
-        <v>90.64560413048611</v>
+        <v>90.78386857282524</v>
       </c>
       <c r="E84">
-        <v>76.09220000000001</v>
+        <v>77.05930000000001</v>
       </c>
       <c r="F84">
-        <v>79.3022</v>
+        <v>80.2693</v>
       </c>
       <c r="G84">
         <v>16.1</v>
@@ -8431,28 +8431,28 @@
         <v>16.7</v>
       </c>
       <c r="M84">
-        <v>5.083271020000001</v>
+        <v>5.145262130000001</v>
       </c>
       <c r="N84">
-        <v>11.61672898</v>
+        <v>11.55473787</v>
       </c>
       <c r="O84">
-        <v>2.5556803756</v>
+        <v>2.5420423314</v>
       </c>
       <c r="P84">
-        <v>9.061048604399998</v>
+        <v>9.012695538599999</v>
       </c>
       <c r="Q84">
-        <v>11.5610486044</v>
+        <v>11.5126955386</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3523934816036575</v>
+        <v>0.3695570129999523</v>
       </c>
       <c r="T84">
-        <v>4.461308730128692</v>
+        <v>4.711059025071735</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.28528617386212</v>
+        <v>3.245704412731251</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1043230322099919</v>
+        <v>0.1042168777313254</v>
       </c>
       <c r="C85">
-        <v>26.61456857282523</v>
+        <v>25.78615545727973</v>
       </c>
       <c r="D85">
-        <v>90.78386857282524</v>
+        <v>90.92255545727974</v>
       </c>
       <c r="E85">
-        <v>77.05930000000001</v>
+        <v>78.02640000000001</v>
       </c>
       <c r="F85">
-        <v>80.2693</v>
+        <v>81.2364</v>
       </c>
       <c r="G85">
         <v>16.1</v>
@@ -8513,28 +8513,28 @@
         <v>16.7</v>
       </c>
       <c r="M85">
-        <v>5.145262130000001</v>
+        <v>5.207253240000001</v>
       </c>
       <c r="N85">
-        <v>11.55473787</v>
+        <v>11.49274676</v>
       </c>
       <c r="O85">
-        <v>2.5420423314</v>
+        <v>2.5284042872</v>
       </c>
       <c r="P85">
-        <v>9.012695538599999</v>
+        <v>8.964342472799999</v>
       </c>
       <c r="Q85">
-        <v>11.5126955386</v>
+        <v>11.4643424728</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3695570129999523</v>
+        <v>0.3888659858207838</v>
       </c>
       <c r="T85">
-        <v>4.711059025071735</v>
+        <v>4.992028106882657</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.245704412731251</v>
+        <v>3.207065074484451</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1042168777313254</v>
+        <v>0.1041107232526589</v>
       </c>
       <c r="C86">
-        <v>25.78615545727975</v>
+        <v>24.95816672285548</v>
       </c>
       <c r="D86">
-        <v>90.92255545727974</v>
+        <v>91.06166672285546</v>
       </c>
       <c r="E86">
-        <v>78.0264</v>
+        <v>78.9935</v>
       </c>
       <c r="F86">
-        <v>81.23639999999999</v>
+        <v>82.20349999999999</v>
       </c>
       <c r="G86">
         <v>16.1</v>
@@ -8595,28 +8595,28 @@
         <v>16.7</v>
       </c>
       <c r="M86">
-        <v>5.20725324</v>
+        <v>5.26924435</v>
       </c>
       <c r="N86">
-        <v>11.49274676</v>
+        <v>11.43075565</v>
       </c>
       <c r="O86">
-        <v>2.5284042872</v>
+        <v>2.514766243</v>
       </c>
       <c r="P86">
-        <v>8.964342472799999</v>
+        <v>8.915989406999998</v>
       </c>
       <c r="Q86">
-        <v>11.4643424728</v>
+        <v>11.415989407</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3888659858207836</v>
+        <v>0.4107494883510593</v>
       </c>
       <c r="T86">
-        <v>4.992028106882653</v>
+        <v>5.310459732935031</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.207065074484451</v>
+        <v>3.169334897137575</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1041107232526589</v>
+        <v>0.1040045687739924</v>
       </c>
       <c r="C87">
-        <v>24.95816672285548</v>
+        <v>24.13060432044323</v>
       </c>
       <c r="D87">
-        <v>91.06166672285546</v>
+        <v>91.20120432044322</v>
       </c>
       <c r="E87">
-        <v>78.9935</v>
+        <v>79.9606</v>
       </c>
       <c r="F87">
-        <v>82.20349999999999</v>
+        <v>83.17059999999999</v>
       </c>
       <c r="G87">
         <v>16.1</v>
@@ -8677,28 +8677,28 @@
         <v>16.7</v>
       </c>
       <c r="M87">
-        <v>5.26924435</v>
+        <v>5.33123546</v>
       </c>
       <c r="N87">
-        <v>11.43075565</v>
+        <v>11.36876454</v>
       </c>
       <c r="O87">
-        <v>2.514766243</v>
+        <v>2.5011281988</v>
       </c>
       <c r="P87">
-        <v>8.915989406999998</v>
+        <v>8.867636341199999</v>
       </c>
       <c r="Q87">
-        <v>11.415989407</v>
+        <v>11.3676363412</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4107494883510593</v>
+        <v>0.4357592055285172</v>
       </c>
       <c r="T87">
-        <v>5.310459732935031</v>
+        <v>5.674381591280604</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.169334897137575</v>
+        <v>3.13248216577551</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1040045687739924</v>
+        <v>0.1038984142953259</v>
       </c>
       <c r="C88">
-        <v>24.13060432044323</v>
+        <v>23.30347021290987</v>
       </c>
       <c r="D88">
-        <v>91.20120432044322</v>
+        <v>91.34117021290986</v>
       </c>
       <c r="E88">
-        <v>79.9606</v>
+        <v>80.9277</v>
       </c>
       <c r="F88">
-        <v>83.17059999999999</v>
+        <v>84.1377</v>
       </c>
       <c r="G88">
         <v>16.1</v>
@@ -8759,28 +8759,28 @@
         <v>16.7</v>
       </c>
       <c r="M88">
-        <v>5.33123546</v>
+        <v>5.39322657</v>
       </c>
       <c r="N88">
-        <v>11.36876454</v>
+        <v>11.30677343</v>
       </c>
       <c r="O88">
-        <v>2.5011281988</v>
+        <v>2.4874901546</v>
       </c>
       <c r="P88">
-        <v>8.867636341199999</v>
+        <v>8.8192832754</v>
       </c>
       <c r="Q88">
-        <v>11.3676363412</v>
+        <v>11.3192832754</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4357592055285172</v>
+        <v>0.4646165715025071</v>
       </c>
       <c r="T88">
-        <v>5.674381591280604</v>
+        <v>6.09429142783319</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.13248216577551</v>
+        <v>3.09647662364016</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1038984142953259</v>
+        <v>0.1037922598166595</v>
       </c>
       <c r="C89">
-        <v>23.30347021290987</v>
+        <v>22.47676637519031</v>
       </c>
       <c r="D89">
-        <v>91.34117021290986</v>
+        <v>91.48156637519031</v>
       </c>
       <c r="E89">
-        <v>80.9277</v>
+        <v>81.8948</v>
       </c>
       <c r="F89">
-        <v>84.1377</v>
+        <v>85.1048</v>
       </c>
       <c r="G89">
         <v>16.1</v>
@@ -8841,28 +8841,28 @@
         <v>16.7</v>
       </c>
       <c r="M89">
-        <v>5.39322657</v>
+        <v>5.455217680000001</v>
       </c>
       <c r="N89">
-        <v>11.30677343</v>
+        <v>11.24478232</v>
       </c>
       <c r="O89">
-        <v>2.4874901546</v>
+        <v>2.4738521104</v>
       </c>
       <c r="P89">
-        <v>8.8192832754</v>
+        <v>8.770930209599999</v>
       </c>
       <c r="Q89">
-        <v>11.3192832754</v>
+        <v>11.2709302096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4646165715025071</v>
+        <v>0.4982834984721621</v>
       </c>
       <c r="T89">
-        <v>6.09429142783319</v>
+        <v>6.58418623714454</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.09647662364016</v>
+        <v>3.061289389280612</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1037922598166595</v>
+        <v>0.103686105337993</v>
       </c>
       <c r="C90">
-        <v>22.47676637519031</v>
+        <v>21.65049479438065</v>
       </c>
       <c r="D90">
-        <v>91.48156637519031</v>
+        <v>91.62239479438064</v>
       </c>
       <c r="E90">
-        <v>81.8948</v>
+        <v>82.86190000000001</v>
       </c>
       <c r="F90">
-        <v>85.1048</v>
+        <v>86.0719</v>
       </c>
       <c r="G90">
         <v>16.1</v>
@@ -8923,28 +8923,28 @@
         <v>16.7</v>
       </c>
       <c r="M90">
-        <v>5.455217680000001</v>
+        <v>5.517208790000001</v>
       </c>
       <c r="N90">
-        <v>11.24478232</v>
+        <v>11.18279121</v>
       </c>
       <c r="O90">
-        <v>2.4738521104</v>
+        <v>2.460214066199999</v>
       </c>
       <c r="P90">
-        <v>8.770930209599999</v>
+        <v>8.722577143799999</v>
       </c>
       <c r="Q90">
-        <v>11.2709302096</v>
+        <v>11.2225771438</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4982834984721621</v>
+        <v>0.5380716848908451</v>
       </c>
       <c r="T90">
-        <v>6.58418623714454</v>
+        <v>7.163152829967045</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.061289389280612</v>
+        <v>3.026892879288695</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.103686105337993</v>
+        <v>0.1090555508593265</v>
       </c>
       <c r="C91">
-        <v>21.65049479438065</v>
+        <v>14.06451186773141</v>
       </c>
       <c r="D91">
-        <v>91.62239479438064</v>
+        <v>85.0035118677314</v>
       </c>
       <c r="E91">
-        <v>82.86190000000001</v>
+        <v>83.82900000000001</v>
       </c>
       <c r="F91">
-        <v>86.0719</v>
+        <v>87.039</v>
       </c>
       <c r="G91">
         <v>16.1</v>
@@ -9005,45 +9005,45 @@
         <v>16.7</v>
       </c>
       <c r="M91">
-        <v>5.517208790000001</v>
+        <v>6.258104100000001</v>
       </c>
       <c r="N91">
-        <v>11.18279121</v>
+        <v>10.4418959</v>
       </c>
       <c r="O91">
-        <v>2.460214066199999</v>
+        <v>2.297217098</v>
       </c>
       <c r="P91">
-        <v>8.722577143799999</v>
+        <v>8.144678802</v>
       </c>
       <c r="Q91">
-        <v>11.2225771438</v>
+        <v>10.644678802</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5380716848908451</v>
+        <v>0.5858175085932649</v>
       </c>
       <c r="T91">
-        <v>7.163152829967045</v>
+        <v>7.857912741354051</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.026892879288695</v>
+        <v>2.668539821828786</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1090555508593265</v>
+        <v>0.10901023638066</v>
       </c>
       <c r="C92">
-        <v>14.06451186773141</v>
+        <v>13.14926706982175</v>
       </c>
       <c r="D92">
-        <v>85.0035118677314</v>
+        <v>85.05536706982176</v>
       </c>
       <c r="E92">
-        <v>83.82900000000001</v>
+        <v>84.79610000000001</v>
       </c>
       <c r="F92">
-        <v>87.039</v>
+        <v>88.0061</v>
       </c>
       <c r="G92">
         <v>16.1</v>
@@ -9087,28 +9087,28 @@
         <v>16.7</v>
       </c>
       <c r="M92">
-        <v>6.258104100000001</v>
+        <v>6.327638590000001</v>
       </c>
       <c r="N92">
-        <v>10.4418959</v>
+        <v>10.37236141</v>
       </c>
       <c r="O92">
-        <v>2.297217098</v>
+        <v>2.281919510199999</v>
       </c>
       <c r="P92">
-        <v>8.144678802</v>
+        <v>8.090441899799998</v>
       </c>
       <c r="Q92">
-        <v>10.644678802</v>
+        <v>10.5904418998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5858175085932649</v>
+        <v>0.6441735153406668</v>
       </c>
       <c r="T92">
-        <v>7.857912741354051</v>
+        <v>8.707063744160392</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.668539821828786</v>
+        <v>2.639215208402096</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.10901023638066</v>
+        <v>0.1089649219019935</v>
       </c>
       <c r="C93">
-        <v>13.14926706982175</v>
+        <v>12.23408557761064</v>
       </c>
       <c r="D93">
-        <v>85.05536706982176</v>
+        <v>85.10728557761063</v>
       </c>
       <c r="E93">
-        <v>84.79610000000001</v>
+        <v>85.7632</v>
       </c>
       <c r="F93">
-        <v>88.0061</v>
+        <v>88.97319999999999</v>
       </c>
       <c r="G93">
         <v>16.1</v>
@@ -9169,28 +9169,28 @@
         <v>16.7</v>
       </c>
       <c r="M93">
-        <v>6.327638590000001</v>
+        <v>6.39717308</v>
       </c>
       <c r="N93">
-        <v>10.37236141</v>
+        <v>10.30282692</v>
       </c>
       <c r="O93">
-        <v>2.281919510199999</v>
+        <v>2.2666219224</v>
       </c>
       <c r="P93">
-        <v>8.090441899799998</v>
+        <v>8.036204997599999</v>
       </c>
       <c r="Q93">
-        <v>10.5904418998</v>
+        <v>10.5362049976</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6441735153406668</v>
+        <v>0.7171185237749194</v>
       </c>
       <c r="T93">
-        <v>8.707063744160392</v>
+        <v>9.768502497668319</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.639215208402096</v>
+        <v>2.610528086571639</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1089649219019935</v>
+        <v>0.108919607423327</v>
       </c>
       <c r="C94">
-        <v>12.23408557761064</v>
+        <v>11.31896750709585</v>
       </c>
       <c r="D94">
-        <v>85.10728557761063</v>
+        <v>85.15926750709585</v>
       </c>
       <c r="E94">
-        <v>85.7632</v>
+        <v>86.7303</v>
       </c>
       <c r="F94">
-        <v>88.97319999999999</v>
+        <v>89.94029999999999</v>
       </c>
       <c r="G94">
         <v>16.1</v>
@@ -9251,28 +9251,28 @@
         <v>16.7</v>
       </c>
       <c r="M94">
-        <v>6.39717308</v>
+        <v>6.46670757</v>
       </c>
       <c r="N94">
-        <v>10.30282692</v>
+        <v>10.23329243</v>
       </c>
       <c r="O94">
-        <v>2.2666219224</v>
+        <v>2.2513243346</v>
       </c>
       <c r="P94">
-        <v>8.036204997599999</v>
+        <v>7.981968095399999</v>
       </c>
       <c r="Q94">
-        <v>10.5362049976</v>
+        <v>10.4819680954</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7171185237749194</v>
+        <v>0.8109049631903867</v>
       </c>
       <c r="T94">
-        <v>9.768502497668319</v>
+        <v>11.13320946646422</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.610528086571639</v>
+        <v>2.582457892092374</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.108919607423327</v>
+        <v>0.1088742929446606</v>
       </c>
       <c r="C95">
-        <v>11.31896750709585</v>
+        <v>10.40391297455878</v>
       </c>
       <c r="D95">
-        <v>85.15926750709585</v>
+        <v>85.21131297455877</v>
       </c>
       <c r="E95">
-        <v>86.7303</v>
+        <v>87.6974</v>
       </c>
       <c r="F95">
-        <v>89.94029999999999</v>
+        <v>90.9074</v>
       </c>
       <c r="G95">
         <v>16.1</v>
@@ -9333,28 +9333,28 @@
         <v>16.7</v>
       </c>
       <c r="M95">
-        <v>6.46670757</v>
+        <v>6.53624206</v>
       </c>
       <c r="N95">
-        <v>10.23329243</v>
+        <v>10.16375794</v>
       </c>
       <c r="O95">
-        <v>2.2513243346</v>
+        <v>2.2360267468</v>
       </c>
       <c r="P95">
-        <v>7.981968095399999</v>
+        <v>7.9277311932</v>
       </c>
       <c r="Q95">
-        <v>10.4819680954</v>
+        <v>10.4277311932</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8109049631903867</v>
+        <v>0.9359535490776768</v>
       </c>
       <c r="T95">
-        <v>11.13320946646422</v>
+        <v>12.9528187581921</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.582457892092374</v>
+        <v>2.554984935793519</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1088742929446606</v>
+        <v>0.1088289784659941</v>
       </c>
       <c r="C96">
-        <v>10.40391297455878</v>
+        <v>9.488922096565162</v>
       </c>
       <c r="D96">
-        <v>85.21131297455877</v>
+        <v>85.26342209656515</v>
       </c>
       <c r="E96">
-        <v>87.6974</v>
+        <v>88.6645</v>
       </c>
       <c r="F96">
-        <v>90.9074</v>
+        <v>91.8745</v>
       </c>
       <c r="G96">
         <v>16.1</v>
@@ -9415,28 +9415,28 @@
         <v>16.7</v>
       </c>
       <c r="M96">
-        <v>6.53624206</v>
+        <v>6.605776550000001</v>
       </c>
       <c r="N96">
-        <v>10.16375794</v>
+        <v>10.09422345</v>
       </c>
       <c r="O96">
-        <v>2.2360267468</v>
+        <v>2.220729158999999</v>
       </c>
       <c r="P96">
-        <v>7.9277311932</v>
+        <v>7.873494290999998</v>
       </c>
       <c r="Q96">
-        <v>10.4277311932</v>
+        <v>10.373494291</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9359535490776768</v>
+        <v>1.111021569319883</v>
       </c>
       <c r="T96">
-        <v>12.9528187581921</v>
+        <v>15.50027176661113</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.554984935793519</v>
+        <v>2.528090357522008</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1088289784659941</v>
+        <v>0.1087836639873276</v>
       </c>
       <c r="C97">
-        <v>9.488922096565162</v>
+        <v>8.573994989966167</v>
       </c>
       <c r="D97">
-        <v>85.26342209656515</v>
+        <v>85.31559498996617</v>
       </c>
       <c r="E97">
-        <v>88.6645</v>
+        <v>89.63160000000001</v>
       </c>
       <c r="F97">
-        <v>91.8745</v>
+        <v>92.8416</v>
       </c>
       <c r="G97">
         <v>16.1</v>
@@ -9497,28 +9497,28 @@
         <v>16.7</v>
       </c>
       <c r="M97">
-        <v>6.605776550000001</v>
+        <v>6.67531104</v>
       </c>
       <c r="N97">
-        <v>10.09422345</v>
+        <v>10.02468896</v>
       </c>
       <c r="O97">
-        <v>2.220729158999999</v>
+        <v>2.2054315712</v>
       </c>
       <c r="P97">
-        <v>7.873494290999998</v>
+        <v>7.819257388799999</v>
       </c>
       <c r="Q97">
-        <v>10.373494291</v>
+        <v>10.3192573888</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.111021569319883</v>
+        <v>1.373623599683192</v>
       </c>
       <c r="T97">
-        <v>15.50027176661113</v>
+        <v>19.32145127923967</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.528090357522008</v>
+        <v>2.501756082964487</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1087836639873276</v>
+        <v>0.1116890895086611</v>
       </c>
       <c r="C98">
-        <v>8.573994989966181</v>
+        <v>4.386046553135571</v>
       </c>
       <c r="D98">
-        <v>85.31559498996617</v>
+        <v>82.09474655313556</v>
       </c>
       <c r="E98">
-        <v>89.63159999999999</v>
+        <v>90.59869999999999</v>
       </c>
       <c r="F98">
-        <v>92.84159999999999</v>
+        <v>93.80869999999999</v>
       </c>
       <c r="G98">
         <v>16.1</v>
@@ -9579,45 +9579,45 @@
         <v>16.7</v>
       </c>
       <c r="M98">
-        <v>6.67531104</v>
+        <v>7.110699459999999</v>
       </c>
       <c r="N98">
-        <v>10.02468896</v>
+        <v>9.58930054</v>
       </c>
       <c r="O98">
-        <v>2.2054315712</v>
+        <v>2.1096461188</v>
       </c>
       <c r="P98">
-        <v>7.819257388799999</v>
+        <v>7.479654421199999</v>
       </c>
       <c r="Q98">
-        <v>10.3192573888</v>
+        <v>9.979654421199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.373623599683189</v>
+        <v>1.811293650288702</v>
       </c>
       <c r="T98">
-        <v>19.32145127923962</v>
+        <v>25.69008380028716</v>
       </c>
       <c r="U98">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V98">
         <v>0.22</v>
       </c>
       <c r="W98">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y98">
-        <v>2.501756082964488</v>
+        <v>2.348573455247679</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1116890895086611</v>
+        <v>0.1116741950299946</v>
       </c>
       <c r="C99">
-        <v>4.386046553135571</v>
+        <v>3.434837758855494</v>
       </c>
       <c r="D99">
-        <v>82.09474655313556</v>
+        <v>82.11063775885547</v>
       </c>
       <c r="E99">
-        <v>90.59869999999999</v>
+        <v>91.5658</v>
       </c>
       <c r="F99">
-        <v>93.80869999999999</v>
+        <v>94.77579999999999</v>
       </c>
       <c r="G99">
         <v>16.1</v>
@@ -9661,28 +9661,28 @@
         <v>16.7</v>
       </c>
       <c r="M99">
-        <v>7.110699459999999</v>
+        <v>7.18400564</v>
       </c>
       <c r="N99">
-        <v>9.58930054</v>
+        <v>9.515994360000001</v>
       </c>
       <c r="O99">
-        <v>2.1096461188</v>
+        <v>2.0935187592</v>
       </c>
       <c r="P99">
-        <v>7.479654421199999</v>
+        <v>7.4224756008</v>
       </c>
       <c r="Q99">
-        <v>9.979654421199999</v>
+        <v>9.9224756008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.811293650288702</v>
+        <v>2.68663375149973</v>
       </c>
       <c r="T99">
-        <v>25.69008380028716</v>
+        <v>38.42734884238224</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.348573455247679</v>
+        <v>2.324608419990049</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1116741950299946</v>
+        <v>0.1116593005513282</v>
       </c>
       <c r="C100">
-        <v>3.434837758855494</v>
+        <v>2.483635117936529</v>
       </c>
       <c r="D100">
-        <v>82.11063775885547</v>
+        <v>82.12653511793653</v>
       </c>
       <c r="E100">
-        <v>91.5658</v>
+        <v>92.5329</v>
       </c>
       <c r="F100">
-        <v>94.77579999999999</v>
+        <v>95.74289999999999</v>
       </c>
       <c r="G100">
         <v>16.1</v>
@@ -9743,28 +9743,28 @@
         <v>16.7</v>
       </c>
       <c r="M100">
-        <v>7.18400564</v>
+        <v>7.25731182</v>
       </c>
       <c r="N100">
-        <v>9.515994360000001</v>
+        <v>9.442688179999999</v>
       </c>
       <c r="O100">
-        <v>2.0935187592</v>
+        <v>2.0773913996</v>
       </c>
       <c r="P100">
-        <v>7.4224756008</v>
+        <v>7.3652967804</v>
       </c>
       <c r="Q100">
-        <v>9.9224756008</v>
+        <v>9.8652967804</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.68663375149973</v>
+        <v>5.312654055132811</v>
       </c>
       <c r="T100">
-        <v>38.42734884238224</v>
+        <v>76.6391439686675</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.324608419990049</v>
+        <v>2.301127526858836</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1116593005513282</v>
-      </c>
-      <c r="C101">
-        <v>2.483635117936529</v>
-      </c>
-      <c r="D101">
-        <v>82.12653511793653</v>
-      </c>
-      <c r="E101">
-        <v>92.5329</v>
-      </c>
-      <c r="F101">
-        <v>95.74289999999999</v>
-      </c>
-      <c r="G101">
-        <v>16.1</v>
-      </c>
-      <c r="H101">
-        <v>93.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>19.2</v>
-      </c>
-      <c r="K101">
-        <v>2.5</v>
-      </c>
-      <c r="L101">
-        <v>16.7</v>
-      </c>
-      <c r="M101">
-        <v>7.25731182</v>
-      </c>
-      <c r="N101">
-        <v>9.442688179999999</v>
-      </c>
-      <c r="O101">
-        <v>2.0773913996</v>
-      </c>
-      <c r="P101">
-        <v>7.3652967804</v>
-      </c>
-      <c r="Q101">
-        <v>9.8652967804</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.312654055132811</v>
-      </c>
-      <c r="T101">
-        <v>76.6391439686675</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.05912400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.301127526858836</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
